--- a/Swerdlow_Management_Platform.xlsx
+++ b/Swerdlow_Management_Platform.xlsx
@@ -29,36 +29,38 @@
     <definedName name="Growth_Rows">'Master Assumptions'!$A$5:$A$9</definedName>
     <definedName name="SelectedProject">'Cockpit'!$C$5</definedName>
     <definedName name="Console_Notes">'Cockpit'!$C$7</definedName>
-    <definedName name="Closing_Date_Cell">'Cockpit'!$D$17</definedName>
-    <definedName name="GSF_Cell">'Cockpit'!$D$18</definedName>
-    <definedName name="NSF_Cell">'Cockpit'!$D$19</definedName>
-    <definedName name="HasComm_Cell">'Cockpit'!$D$26</definedName>
-    <definedName name="CommSF_Cell">'Cockpit'!$D$27</definedName>
-    <definedName name="CommPSF_Cell">'Cockpit'!$D$28</definedName>
-    <definedName name="CommVac_Cell">'Cockpit'!$D$31</definedName>
-    <definedName name="CommOpEx_Cell">'Cockpit'!$D$32</definedName>
-    <definedName name="CommNOI_In">'Cockpit'!$E$33</definedName>
-    <definedName name="CommNOI_Cur">'Cockpit'!$J$33</definedName>
-    <definedName name="Units_Total">'Cockpit'!$C$40</definedName>
-    <definedName name="Units_Total_Cur">'Cockpit'!$H$40</definedName>
-    <definedName name="Blended_PUPM">'Cockpit'!$E$40</definedName>
-    <definedName name="Blended_PUPM_Cur">'Cockpit'!$J$40</definedName>
-    <definedName name="AvgSF_In">'Cockpit'!$D$40</definedName>
-    <definedName name="GPR_In">'Cockpit'!$E$42</definedName>
-    <definedName name="GPR_Cur">'Cockpit'!$J$42</definedName>
-    <definedName name="ERR_In">'Cockpit'!$E$47</definedName>
-    <definedName name="ERR_Cur">'Cockpit'!$J$47</definedName>
-    <definedName name="OtherInc_In">'Cockpit'!$E$55</definedName>
-    <definedName name="OtherInc_Cur">'Cockpit'!$J$55</definedName>
-    <definedName name="EGR_In">'Cockpit'!$E$57</definedName>
-    <definedName name="EGR_Cur">'Cockpit'!$J$57</definedName>
-    <definedName name="TotOpEx_In">'Cockpit'!$E$70</definedName>
-    <definedName name="TotOpEx_Cur">'Cockpit'!$J$70</definedName>
-    <definedName name="NOI_In">'Cockpit'!$E$73</definedName>
-    <definedName name="NOI_Cur">'Cockpit'!$J$73</definedName>
-    <definedName name="OpExRatio_In">'Cockpit'!$E$74</definedName>
-    <definedName name="TDC_In">'Cockpit'!$E$90</definedName>
-    <definedName name="TDC_Cur">'Cockpit'!$J$90</definedName>
+    <definedName name="LandAcres_Cell">'Cockpit'!$D$19</definedName>
+    <definedName name="Closing_Date_Cell">'Cockpit'!$D$20</definedName>
+    <definedName name="GSF_Cell">'Cockpit'!$D$21</definedName>
+    <definedName name="NSF_Cell">'Cockpit'!$D$22</definedName>
+    <definedName name="ExitCap_Cell">'Cockpit'!$D$23</definedName>
+    <definedName name="HasComm_Cell">'Cockpit'!$D$30</definedName>
+    <definedName name="CommSF_Cell">'Cockpit'!$D$31</definedName>
+    <definedName name="CommPSF_Cell">'Cockpit'!$D$32</definedName>
+    <definedName name="CommVac_Cell">'Cockpit'!$D$35</definedName>
+    <definedName name="CommOpEx_Cell">'Cockpit'!$D$36</definedName>
+    <definedName name="CommNOI_In">'Cockpit'!$E$37</definedName>
+    <definedName name="CommNOI_Cur">'Cockpit'!$J$37</definedName>
+    <definedName name="Units_Total">'Cockpit'!$C$44</definedName>
+    <definedName name="Units_Total_Cur">'Cockpit'!$H$44</definedName>
+    <definedName name="Blended_PUPM">'Cockpit'!$E$44</definedName>
+    <definedName name="Blended_PUPM_Cur">'Cockpit'!$J$44</definedName>
+    <definedName name="AvgSF_In">'Cockpit'!$D$44</definedName>
+    <definedName name="GPR_In">'Cockpit'!$E$46</definedName>
+    <definedName name="GPR_Cur">'Cockpit'!$J$46</definedName>
+    <definedName name="ERR_In">'Cockpit'!$E$51</definedName>
+    <definedName name="ERR_Cur">'Cockpit'!$J$51</definedName>
+    <definedName name="OtherInc_In">'Cockpit'!$E$59</definedName>
+    <definedName name="OtherInc_Cur">'Cockpit'!$J$59</definedName>
+    <definedName name="EGR_In">'Cockpit'!$E$61</definedName>
+    <definedName name="EGR_Cur">'Cockpit'!$J$61</definedName>
+    <definedName name="TotOpEx_In">'Cockpit'!$E$74</definedName>
+    <definedName name="TotOpEx_Cur">'Cockpit'!$J$74</definedName>
+    <definedName name="NOI_In">'Cockpit'!$E$77</definedName>
+    <definedName name="NOI_Cur">'Cockpit'!$J$77</definedName>
+    <definedName name="OpExRatio_In">'Cockpit'!$E$78</definedName>
+    <definedName name="TDC_In">'Cockpit'!$E$94</definedName>
+    <definedName name="TDC_Cur">'Cockpit'!$J$94</definedName>
     <definedName name="MaxRecordsPerProject">'Database'!$B$2</definedName>
     <definedName name="SelectedProjectDash">'Project Dashboard'!$B$3</definedName>
   </definedNames>
@@ -72,9 +74,9 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -160,12 +162,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
@@ -173,7 +169,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,6 +196,12 @@
     <font>
       <name val="Arial"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -354,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -412,27 +414,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -452,7 +462,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -472,6 +482,13 @@
     <xf numFmtId="166" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -482,40 +499,33 @@
     <xf numFmtId="168" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -530,10 +540,10 @@
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -564,12 +574,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -578,22 +588,19 @@
     <xf numFmtId="165" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -603,7 +610,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,7 +1125,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J90"/>
+  <dimension ref="B2:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1223,7 +1230,7 @@
     <row r="9">
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>KPIs (from working inputs)</t>
+          <t>KEY METRICS  -  Returns &amp; Value   (from working blue inputs; IRR / equity multiple / cash-on-cash arrive with the CF engine)</t>
         </is>
       </c>
       <c r="C9" s="21" t="n"/>
@@ -1234,1947 +1241,2068 @@
       <c r="H9" s="21" t="n"/>
       <c r="I9" s="21" t="n"/>
       <c r="J9" s="21" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
+      <c r="K9" s="21" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Total Units</t>
+          <t>Untrended Yield on Cost</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Total NSF</t>
+          <t>Dev Spread (YoC - Cap)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
+          <t>Exit Cap Rate</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Stabilized Value</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Development Profit</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Development Margin</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>NOI</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
           <t>EGR</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>NOI</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>OpEx Ratio</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>NOI/Unit</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>Total Dev Cost</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>Cost/Unit</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>Yield on Cost</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="23">
+        <f>IFERROR(NOI_In/TDC_In,0)</f>
+        <v/>
+      </c>
+      <c r="C11" s="23">
+        <f>IFERROR(NOI_In/TDC_In,0)-ExitCap_Cell</f>
+        <v/>
+      </c>
+      <c r="D11" s="23">
+        <f>ExitCap_Cell</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>IFERROR(NOI_In/ExitCap_Cell,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(NOI_In/ExitCap_Cell,0)-TDC_In</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IFERROR((NOI_In/ExitCap_Cell-TDC_In)/TDC_In,0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
+        <f>NOI_In</f>
+        <v/>
+      </c>
+      <c r="J11" s="24">
+        <f>EGR_In</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
+        <f>OpExRatio_In</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>KEY METRICS  -  Cost &amp; Physical</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Total Dev Cost</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Cost / Unit</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Cost / GSF</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Value / Unit</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>Units / Acre</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>FAR</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Efficiency (NSF/GSF)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>Avg Unit SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="24">
+        <f>TDC_In</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>IFERROR(TDC_In/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>IFERROR(TDC_In/N(GSF_Cell),0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>IFERROR((NOI_In/ExitCap_Cell)/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="27">
         <f>Units_Total</f>
         <v/>
       </c>
-      <c r="C11" s="23">
-        <f>NSF_Cell</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>EGR_In</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>NOI_In</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>OpExRatio_In</f>
-        <v/>
-      </c>
-      <c r="G11" s="24">
-        <f>IFERROR(NOI_In/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="24">
-        <f>TDC_In</f>
-        <v/>
-      </c>
-      <c r="I11" s="24">
-        <f>IFERROR(TDC_In/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="25">
-        <f>IFERROR(NOI_In/TDC_In,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="26" t="inlineStr">
+      <c r="H14" s="28">
+        <f>IFERROR(Units_Total/N(LandAcres_Cell),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="28">
+        <f>IFERROR(N(GSF_Cell)/(N(LandAcres_Cell)*43560),0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="25">
+        <f>IFERROR(N(NSF_Cell)/N(GSF_Cell),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="27">
+        <f>AvgSF_In</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>General Inputs</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>Input  |  Current -&gt;</t>
         </is>
       </c>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="B14" s="29" t="inlineStr">
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="21" t="n"/>
+      <c r="J16" s="21" t="n"/>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Phase No.</t>
         </is>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D17" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="31" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>Phase No.</t>
         </is>
       </c>
-      <c r="I14" s="32">
+      <c r="I17" s="34">
         <f>IFERROR(INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="15" outlineLevel="1">
-      <c r="B15" s="29" t="inlineStr">
+    <row r="18" outlineLevel="1">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>RAD 1</t>
         </is>
       </c>
-      <c r="F15" s="34">
-        <f>IF(D15="","!","")</f>
-        <v/>
-      </c>
-      <c r="G15" s="31" t="inlineStr">
+      <c r="F18" s="36">
+        <f>IF(D18="","!","")</f>
+        <v/>
+      </c>
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="I15" s="35">
+      <c r="I18" s="37">
         <f>IFERROR(INDEX(Database!$H:$H,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="16" outlineLevel="1">
-      <c r="B16" s="29" t="inlineStr">
+    <row r="19" outlineLevel="1">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>Land Size (Acres)</t>
         </is>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D19" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="31" t="inlineStr">
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t>Land Size (Acres)</t>
         </is>
       </c>
-      <c r="I16" s="37">
+      <c r="I19" s="39">
         <f>IFERROR(INDEX(Database!$I:$I,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="17" outlineLevel="1">
-      <c r="B17" s="29" t="inlineStr">
+    <row r="20" outlineLevel="1">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Closing Date</t>
         </is>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D20" s="40" t="n">
         <v>46204</v>
       </c>
-      <c r="F17" s="34">
-        <f>IF(N(D17)=0,"!","")</f>
-        <v/>
-      </c>
-      <c r="G17" s="31" t="inlineStr">
+      <c r="F20" s="36">
+        <f>IF(N(D20)=0,"!","")</f>
+        <v/>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
         <is>
           <t>Closing Date</t>
         </is>
       </c>
-      <c r="I17" s="39">
+      <c r="I20" s="41">
         <f>IFERROR(INDEX(Database!$J:$J,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="18" outlineLevel="1">
-      <c r="B18" s="29" t="inlineStr">
+    <row r="21" outlineLevel="1">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>Gross Building Area (GSF)</t>
         </is>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D21" s="32" t="n">
         <v>240000</v>
       </c>
-      <c r="F18" s="34">
-        <f>IF(N(D18)=0,"!","")</f>
-        <v/>
-      </c>
-      <c r="G18" s="31" t="inlineStr">
+      <c r="F21" s="36">
+        <f>IF(N(D21)=0,"!","")</f>
+        <v/>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>Gross Building Area (GSF)</t>
         </is>
       </c>
-      <c r="I18" s="32">
+      <c r="I21" s="34">
         <f>IFERROR(INDEX(Database!$K:$K,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="19" outlineLevel="1">
-      <c r="B19" s="29" t="inlineStr">
+    <row r="22" outlineLevel="1">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Net Rentable Area (NSF)</t>
         </is>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D22" s="32" t="n">
         <v>200000</v>
       </c>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="G22" s="33" t="inlineStr">
         <is>
           <t>Net Rentable Area (NSF)</t>
         </is>
       </c>
-      <c r="I19" s="32">
+      <c r="I22" s="34">
         <f>IFERROR(INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+    <row r="23" outlineLevel="1">
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>Exit / Stabilized Cap Rate</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>Exit / Stabilized Cap Rate</t>
+        </is>
+      </c>
+      <c r="I23" s="43">
+        <f>IFERROR(INDEX(Database!$M:$M,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Key Dates</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="30" t="inlineStr">
         <is>
           <t>Input  |  Current -&gt;</t>
         </is>
       </c>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-    </row>
-    <row r="21" outlineLevel="1">
-      <c r="B21" s="29" t="inlineStr">
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+    </row>
+    <row r="25" outlineLevel="1">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>Construction Start (month offset)</t>
         </is>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D25" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="40">
-        <f>EDATE(Closing_Date_Cell,D21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="31" t="inlineStr">
+      <c r="E25" s="44">
+        <f>EDATE(Closing_Date_Cell,D25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>Construction Start</t>
         </is>
       </c>
-      <c r="I21" s="32">
-        <f>IFERROR(INDEX(Database!$M:$M,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J21" s="39">
-        <f>IFERROR(EDATE(Closing_Date_Cell,I21),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1">
-      <c r="B22" s="29" t="inlineStr">
+      <c r="I25" s="34">
+        <f>IFERROR(INDEX(Database!$N:$N,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J25" s="41">
+        <f>IFERROR(EDATE(Closing_Date_Cell,I25),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" outlineLevel="1">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Initial Occupancy (month offset)</t>
         </is>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="D26" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="E22" s="40">
-        <f>EDATE(Closing_Date_Cell,D22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="31" t="inlineStr">
+      <c r="E26" s="44">
+        <f>EDATE(Closing_Date_Cell,D26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="33" t="inlineStr">
         <is>
           <t>Initial Occupancy</t>
         </is>
       </c>
-      <c r="I22" s="32">
-        <f>IFERROR(INDEX(Database!$N:$N,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J22" s="39">
-        <f>IFERROR(EDATE(Closing_Date_Cell,I22),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" outlineLevel="1">
-      <c r="B23" s="29" t="inlineStr">
+      <c r="I26" s="34">
+        <f>IFERROR(INDEX(Database!$O:$O,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J26" s="41">
+        <f>IFERROR(EDATE(Closing_Date_Cell,I26),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Construction End (month offset)</t>
         </is>
       </c>
-      <c r="D23" s="30" t="n">
+      <c r="D27" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="40">
-        <f>EDATE(Closing_Date_Cell,D23)</f>
-        <v/>
-      </c>
-      <c r="G23" s="31" t="inlineStr">
+      <c r="E27" s="44">
+        <f>EDATE(Closing_Date_Cell,D27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>Construction End</t>
         </is>
       </c>
-      <c r="I23" s="32">
-        <f>IFERROR(INDEX(Database!$O:$O,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J23" s="39">
-        <f>IFERROR(EDATE(Closing_Date_Cell,I23),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1">
-      <c r="B24" s="29" t="inlineStr">
+      <c r="I27" s="34">
+        <f>IFERROR(INDEX(Database!$P:$P,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J27" s="41">
+        <f>IFERROR(EDATE(Closing_Date_Cell,I27),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>Stabilization (month offset)</t>
         </is>
       </c>
-      <c r="D24" s="30" t="n">
+      <c r="D28" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="E24" s="40">
-        <f>EDATE(Closing_Date_Cell,D24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="31" t="inlineStr">
+      <c r="E28" s="44">
+        <f>EDATE(Closing_Date_Cell,D28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="33" t="inlineStr">
         <is>
           <t>Stabilization</t>
         </is>
       </c>
-      <c r="I24" s="32">
-        <f>IFERROR(INDEX(Database!$P:$P,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J24" s="39">
-        <f>IFERROR(EDATE(Closing_Date_Cell,I24),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="26" t="inlineStr">
+      <c r="I28" s="34">
+        <f>IFERROR(INDEX(Database!$Q:$Q,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J28" s="41">
+        <f>IFERROR(EDATE(Closing_Date_Cell,I28),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Commercial Assumptions</t>
         </is>
       </c>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="30" t="inlineStr">
         <is>
           <t>Input  |  Current -&gt;</t>
         </is>
       </c>
-      <c r="H25" s="27" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="27" t="n"/>
-    </row>
-    <row r="26" outlineLevel="1">
-      <c r="B26" s="29" t="inlineStr">
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="21" t="n"/>
+    </row>
+    <row r="30" outlineLevel="1">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>Has Commercial?</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G26" s="31" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>Has Commercial?</t>
         </is>
       </c>
-      <c r="I26" s="35">
-        <f>IFERROR(INDEX(Database!$Q:$Q,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1">
-      <c r="B27" s="29" t="inlineStr">
+      <c r="I30" s="37">
+        <f>IFERROR(INDEX(Database!$R:$R,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>Commercial Leasable SF</t>
         </is>
       </c>
-      <c r="D27" s="30" t="n">
+      <c r="D31" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="31" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>Commercial Leasable SF</t>
         </is>
       </c>
-      <c r="I27" s="32">
-        <f>IFERROR(INDEX(Database!$R:$R,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" outlineLevel="1">
-      <c r="B28" s="29" t="inlineStr">
+      <c r="I31" s="34">
+        <f>IFERROR(INDEX(Database!$S:$S,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" outlineLevel="1">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>Annual Rent PSF</t>
         </is>
       </c>
-      <c r="D28" s="41" t="n">
+      <c r="D32" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="31" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>Annual Rent PSF</t>
         </is>
       </c>
-      <c r="I28" s="42">
-        <f>IFERROR(INDEX(Database!$S:$S,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" outlineLevel="1">
-      <c r="B29" s="29" t="inlineStr">
+      <c r="I32" s="46">
+        <f>IFERROR(INDEX(Database!$T:$T,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D33" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="G29" s="31" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="I29" s="44">
-        <f>IFERROR(INDEX(Database!$T:$T,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1">
-      <c r="B30" s="29" t="inlineStr">
+      <c r="I33" s="43">
+        <f>IFERROR(INDEX(Database!$U:$U,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>Abatement (months)</t>
         </is>
       </c>
-      <c r="D30" s="30" t="n">
+      <c r="D34" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="31" t="inlineStr">
+      <c r="G34" s="33" t="inlineStr">
         <is>
           <t>Abatement (months)</t>
         </is>
       </c>
-      <c r="I30" s="32">
-        <f>IFERROR(INDEX(Database!$U:$U,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1">
-      <c r="B31" s="29" t="inlineStr">
+      <c r="I34" s="34">
+        <f>IFERROR(INDEX(Database!$V:$V,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>General Vacancy %</t>
         </is>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D35" s="42" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G31" s="31" t="inlineStr">
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t>General Vacancy %</t>
         </is>
       </c>
-      <c r="I31" s="44">
-        <f>IFERROR(INDEX(Database!$V:$V,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" outlineLevel="1">
-      <c r="B32" s="29" t="inlineStr">
+      <c r="I35" s="43">
+        <f>IFERROR(INDEX(Database!$W:$W,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Operating Expenses $/SF</t>
         </is>
       </c>
-      <c r="D32" s="41" t="n">
+      <c r="D36" s="45" t="n">
         <v>6.75</v>
       </c>
-      <c r="G32" s="31" t="inlineStr">
+      <c r="G36" s="33" t="inlineStr">
         <is>
           <t>Operating Expenses $/SF</t>
         </is>
       </c>
-      <c r="I32" s="42">
-        <f>IFERROR(INDEX(Database!$W:$W,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1">
-      <c r="B33" s="45" t="inlineStr">
+      <c r="I36" s="46">
+        <f>IFERROR(INDEX(Database!$X:$X,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1">
+      <c r="B37" s="47" t="inlineStr">
         <is>
           <t>Stabilized Commercial NOI</t>
         </is>
       </c>
-      <c r="E33" s="46">
+      <c r="E37" s="48">
         <f>IF(HasComm_Cell="Yes",CommSF_Cell*CommPSF_Cell*(1-CommVac_Cell)-CommSF_Cell*CommOpEx_Cell,0)</f>
         <v/>
       </c>
-      <c r="G33" s="47" t="inlineStr">
+      <c r="G37" s="49" t="inlineStr">
         <is>
           <t>Stabilized Commercial NOI</t>
         </is>
       </c>
-      <c r="J33" s="48">
-        <f>IFERROR(IF(INDEX(Database!$Q:$Q,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))="Yes",INDEX(Database!$R:$R,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))*INDEX(Database!$S:$S,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))*(1-INDEX(Database!$V:$V,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)))-INDEX(Database!$R:$R,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))*INDEX(Database!$W:$W,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="26" t="inlineStr">
+      <c r="J37" s="50">
+        <f>IFERROR(IF(INDEX(Database!$R:$R,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))="Yes",INDEX(Database!$S:$S,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))*INDEX(Database!$T:$T,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))*(1-INDEX(Database!$W:$W,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)))-INDEX(Database!$S:$S,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0))*INDEX(Database!$X:$X,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),0),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>Multifamily - Unit Mix &amp; Rental Revenue (Exhibit A/C)</t>
         </is>
       </c>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>Input  |  Current -&gt;</t>
         </is>
       </c>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="27" t="n"/>
-    </row>
-    <row r="35" outlineLevel="1">
-      <c r="B35" s="49" t="inlineStr">
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="21" t="n"/>
+      <c r="J38" s="21" t="n"/>
+    </row>
+    <row r="39" outlineLevel="1">
+      <c r="B39" s="51" t="inlineStr">
         <is>
           <t>Unit Type</t>
         </is>
       </c>
-      <c r="C35" s="49" t="inlineStr">
+      <c r="C39" s="51" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D35" s="49" t="inlineStr">
+      <c r="D39" s="51" t="inlineStr">
         <is>
           <t>Avg SF</t>
         </is>
       </c>
-      <c r="E35" s="49" t="inlineStr">
+      <c r="E39" s="51" t="inlineStr">
         <is>
           <t>$ PUPM</t>
         </is>
       </c>
-      <c r="G35" s="49" t="inlineStr">
+      <c r="G39" s="51" t="inlineStr">
         <is>
           <t>Unit Type</t>
         </is>
       </c>
-      <c r="H35" s="49" t="inlineStr">
+      <c r="H39" s="51" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="I35" s="49" t="inlineStr">
+      <c r="I39" s="51" t="inlineStr">
         <is>
           <t>Avg SF</t>
         </is>
       </c>
-      <c r="J35" s="49" t="inlineStr">
+      <c r="J39" s="51" t="inlineStr">
         <is>
           <t>$ PUPM</t>
         </is>
       </c>
     </row>
-    <row r="36" outlineLevel="1">
-      <c r="B36" s="50" t="inlineStr">
+    <row r="40" outlineLevel="1">
+      <c r="B40" s="52" t="inlineStr">
         <is>
           <t>Studio</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E36" s="51" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G36" s="52" t="inlineStr">
+      <c r="C40" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>550</v>
+      </c>
+      <c r="E40" s="53" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G40" s="54" t="inlineStr">
         <is>
           <t>Studio</t>
         </is>
       </c>
-      <c r="H36" s="32">
-        <f>IFERROR(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="I36" s="32">
+      <c r="H40" s="34">
         <f>IFERROR(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
-      <c r="J36" s="53">
+      <c r="I40" s="34">
         <f>IFERROR(INDEX(Database!$AA:$AA,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
-    </row>
-    <row r="37" outlineLevel="1">
-      <c r="B37" s="50" t="inlineStr">
+      <c r="J40" s="55">
+        <f>IFERROR(INDEX(Database!$AB:$AB,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1">
+      <c r="B41" s="52" t="inlineStr">
         <is>
           <t>1 Bedroom</t>
         </is>
       </c>
-      <c r="C37" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E37" s="51" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G37" s="52" t="inlineStr">
+      <c r="C41" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>750</v>
+      </c>
+      <c r="E41" s="53" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G41" s="54" t="inlineStr">
         <is>
           <t>1 Bedroom</t>
         </is>
       </c>
-      <c r="H37" s="32">
-        <f>IFERROR(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="I37" s="32">
+      <c r="H41" s="34">
         <f>IFERROR(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
-      <c r="J37" s="53">
+      <c r="I41" s="34">
         <f>IFERROR(INDEX(Database!$AE:$AE,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
         <v/>
       </c>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="B38" s="50" t="inlineStr">
+      <c r="J41" s="55">
+        <f>IFERROR(INDEX(Database!$AF:$AF,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1">
+      <c r="B42" s="52" t="inlineStr">
         <is>
           <t>2 Bedroom</t>
         </is>
       </c>
-      <c r="C38" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E38" s="51" t="n">
+      <c r="C42" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E42" s="53" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G42" s="54" t="inlineStr">
+        <is>
+          <t>2 Bedroom</t>
+        </is>
+      </c>
+      <c r="H42" s="34">
+        <f>IFERROR(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="I42" s="34">
+        <f>IFERROR(INDEX(Database!$AI:$AI,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J42" s="55">
+        <f>IFERROR(INDEX(Database!$AJ:$AJ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1">
+      <c r="B43" s="52" t="inlineStr">
+        <is>
+          <t>3 Bedroom</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="53" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G43" s="54" t="inlineStr">
+        <is>
+          <t>3 Bedroom</t>
+        </is>
+      </c>
+      <c r="H43" s="34">
+        <f>IFERROR(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="I43" s="34">
+        <f>IFERROR(INDEX(Database!$AM:$AM,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J43" s="55">
+        <f>IFERROR(INDEX(Database!$AN:$AN,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" outlineLevel="1">
+      <c r="B44" s="56" t="inlineStr">
+        <is>
+          <t>Total / Blended</t>
+        </is>
+      </c>
+      <c r="C44" s="57">
+        <f>SUM(C40:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="57">
+        <f>IFERROR(SUMPRODUCT(D40:D43,C40:C43)/C44,0)</f>
+        <v/>
+      </c>
+      <c r="E44" s="48">
+        <f>IFERROR(SUMPRODUCT(E40:E43,C40:C43)/C44,0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="58" t="inlineStr">
+        <is>
+          <t>Total / Blended</t>
+        </is>
+      </c>
+      <c r="H44" s="59">
+        <f>SUM(H40:H43)</f>
+        <v/>
+      </c>
+      <c r="I44" s="59">
+        <f>IFERROR(SUMPRODUCT(I40:I43,H40:H43)/H44,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="50">
+        <f>IFERROR(SUMPRODUCT(J40:J43,H40:H43)/H44,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1"/>
+    <row r="46" outlineLevel="1">
+      <c r="B46" s="47" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent</t>
+        </is>
+      </c>
+      <c r="E46" s="48">
+        <f>Blended_PUPM*Units_Total*12</f>
+        <v/>
+      </c>
+      <c r="G46" s="49" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent</t>
+        </is>
+      </c>
+      <c r="J46" s="50">
+        <f>Blended_PUPM_Cur*Units_Total_Cur*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1">
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>Vacancy</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E47" s="60">
+        <f>-GPR_In*D47</f>
+        <v/>
+      </c>
+      <c r="G47" s="33" t="inlineStr">
+        <is>
+          <t>Vacancy</t>
+        </is>
+      </c>
+      <c r="I47" s="43">
+        <f>IFERROR(INDEX(Database!$AO:$AO,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J47" s="61">
+        <f>-GPR_Cur*I47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1">
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>Concessions</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="60">
+        <f>-GPR_In*D48</f>
+        <v/>
+      </c>
+      <c r="G48" s="33" t="inlineStr">
+        <is>
+          <t>Concessions</t>
+        </is>
+      </c>
+      <c r="I48" s="43">
+        <f>IFERROR(INDEX(Database!$AP:$AP,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J48" s="61">
+        <f>-GPR_Cur*I48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1">
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="60">
+        <f>-GPR_In*D49</f>
+        <v/>
+      </c>
+      <c r="G49" s="33" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="I49" s="43">
+        <f>IFERROR(INDEX(Database!$AQ:$AQ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J49" s="61">
+        <f>-GPR_Cur*I49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" outlineLevel="1">
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>Collection Loss</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="60">
+        <f>-GPR_In*D50</f>
+        <v/>
+      </c>
+      <c r="G50" s="33" t="inlineStr">
+        <is>
+          <t>Collection Loss</t>
+        </is>
+      </c>
+      <c r="I50" s="43">
+        <f>IFERROR(INDEX(Database!$AR:$AR,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J50" s="61">
+        <f>-GPR_Cur*I50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1">
+      <c r="B51" s="47" t="inlineStr">
+        <is>
+          <t>Effective Rental Revenue</t>
+        </is>
+      </c>
+      <c r="E51" s="48">
+        <f>GPR_In+E47+E48+E49+E50</f>
+        <v/>
+      </c>
+      <c r="G51" s="49" t="inlineStr">
+        <is>
+          <t>Effective Rental Revenue</t>
+        </is>
+      </c>
+      <c r="J51" s="50">
+        <f>GPR_Cur+J47+J48+J49+J50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Other Residential Income (Exhibit C)</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>Input  |  Current -&gt;</t>
+        </is>
+      </c>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="21" t="n"/>
+      <c r="J52" s="21" t="n"/>
+    </row>
+    <row r="53" outlineLevel="1">
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D53" s="51" t="inlineStr">
+        <is>
+          <t>$ PUPM</t>
+        </is>
+      </c>
+      <c r="E53" s="51" t="inlineStr">
+        <is>
+          <t>$ Annual</t>
+        </is>
+      </c>
+      <c r="G53" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I53" s="51" t="inlineStr">
+        <is>
+          <t>$ PUPM</t>
+        </is>
+      </c>
+      <c r="J53" s="51" t="inlineStr">
+        <is>
+          <t>$ Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1">
+      <c r="B54" s="52" t="inlineStr">
+        <is>
+          <t>Item 1</t>
+        </is>
+      </c>
+      <c r="D54" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" s="60">
+        <f>N(D54)*12*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G54" s="54" t="inlineStr">
+        <is>
+          <t>Item 1</t>
+        </is>
+      </c>
+      <c r="I54" s="46">
+        <f>IFERROR(INDEX(Database!$AT:$AT,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J54" s="55">
+        <f>N(I54)*12*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1">
+      <c r="B55" s="52" t="inlineStr">
+        <is>
+          <t>Item 2</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr"/>
+      <c r="E55" s="60">
+        <f>N(D55)*12*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G55" s="54" t="inlineStr">
+        <is>
+          <t>Item 2</t>
+        </is>
+      </c>
+      <c r="I55" s="46">
+        <f>IFERROR(INDEX(Database!$AV:$AV,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J55" s="55">
+        <f>N(I55)*12*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="B56" s="52" t="inlineStr">
+        <is>
+          <t>Item 3</t>
+        </is>
+      </c>
+      <c r="D56" s="45" t="inlineStr"/>
+      <c r="E56" s="60">
+        <f>N(D56)*12*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G56" s="54" t="inlineStr">
+        <is>
+          <t>Item 3</t>
+        </is>
+      </c>
+      <c r="I56" s="46">
+        <f>IFERROR(INDEX(Database!$AX:$AX,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J56" s="55">
+        <f>N(I56)*12*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="B57" s="52" t="inlineStr">
+        <is>
+          <t>Item 4</t>
+        </is>
+      </c>
+      <c r="D57" s="45" t="inlineStr"/>
+      <c r="E57" s="60">
+        <f>N(D57)*12*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G57" s="54" t="inlineStr">
+        <is>
+          <t>Item 4</t>
+        </is>
+      </c>
+      <c r="I57" s="46">
+        <f>IFERROR(INDEX(Database!$AZ:$AZ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J57" s="55">
+        <f>N(I57)*12*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="B58" s="52" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="D58" s="45" t="inlineStr"/>
+      <c r="E58" s="60">
+        <f>N(D58)*12*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G58" s="54" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="I58" s="46">
+        <f>IFERROR(INDEX(Database!$BB:$BB,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J58" s="55">
+        <f>N(I58)*12*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="B59" s="56" t="inlineStr">
+        <is>
+          <t>Total Other Income</t>
+        </is>
+      </c>
+      <c r="E59" s="48">
+        <f>SUM(E54:E58)</f>
+        <v/>
+      </c>
+      <c r="G59" s="58" t="inlineStr">
+        <is>
+          <t>Total Other Income</t>
+        </is>
+      </c>
+      <c r="J59" s="50">
+        <f>SUM(J54:J58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1"/>
+    <row r="61" outlineLevel="1">
+      <c r="B61" s="56" t="inlineStr">
+        <is>
+          <t>Effective Gross Revenue (EGR)</t>
+        </is>
+      </c>
+      <c r="E61" s="48">
+        <f>ERR_In+OtherInc_In</f>
+        <v/>
+      </c>
+      <c r="G61" s="58" t="inlineStr">
+        <is>
+          <t>Effective Gross Revenue (EGR)</t>
+        </is>
+      </c>
+      <c r="J61" s="50">
+        <f>ERR_Cur+OtherInc_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1"/>
+    <row r="63">
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>Multifamily Operating Expenses (Exhibit D)</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="30" t="inlineStr">
+        <is>
+          <t>Input  |  Current -&gt;</t>
+        </is>
+      </c>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D64" s="51" t="inlineStr">
+        <is>
+          <t>$ PUPA</t>
+        </is>
+      </c>
+      <c r="E64" s="51" t="inlineStr">
+        <is>
+          <t>$ Annual</t>
+        </is>
+      </c>
+      <c r="G64" s="51" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I64" s="51" t="inlineStr">
+        <is>
+          <t>$ PUPA</t>
+        </is>
+      </c>
+      <c r="J64" s="51" t="inlineStr">
+        <is>
+          <t>$ Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D65" s="53" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E65" s="60">
+        <f>N(D65)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G65" s="33" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="I65" s="55">
+        <f>IFERROR(INDEX(Database!$BC:$BC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J65" s="61">
+        <f>N(I65)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" outlineLevel="1">
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D66" s="53" t="n">
+        <v>350</v>
+      </c>
+      <c r="E66" s="60">
+        <f>N(D66)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G66" s="33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="I66" s="55">
+        <f>IFERROR(INDEX(Database!$BD:$BD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J66" s="61">
+        <f>N(I66)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="D67" s="53" t="n">
+        <v>350</v>
+      </c>
+      <c r="E67" s="60">
+        <f>N(D67)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G67" s="33" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="I67" s="55">
+        <f>IFERROR(INDEX(Database!$BE:$BE,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J67" s="61">
+        <f>N(I67)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" outlineLevel="1">
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="D68" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" s="60">
+        <f>N(D68)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G68" s="33" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="I68" s="55">
+        <f>IFERROR(INDEX(Database!$BF:$BF,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J68" s="61">
+        <f>N(I68)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maint.</t>
+        </is>
+      </c>
+      <c r="D69" s="53" t="n">
+        <v>300</v>
+      </c>
+      <c r="E69" s="60">
+        <f>N(D69)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G69" s="33" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maint.</t>
+        </is>
+      </c>
+      <c r="I69" s="55">
+        <f>IFERROR(INDEX(Database!$BG:$BG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J69" s="61">
+        <f>N(I69)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D70" s="53" t="n">
+        <v>900</v>
+      </c>
+      <c r="E70" s="60">
+        <f>N(D70)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G70" s="33" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I70" s="55">
+        <f>IFERROR(INDEX(Database!$BH:$BH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J70" s="61">
+        <f>N(I70)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D71" s="53" t="n">
         <v>1000</v>
       </c>
-      <c r="G38" s="52" t="inlineStr">
-        <is>
-          <t>2 Bedroom</t>
-        </is>
-      </c>
-      <c r="H38" s="32">
-        <f>IFERROR(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="I38" s="32">
-        <f>IFERROR(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J38" s="53">
-        <f>IFERROR(INDEX(Database!$AI:$AI,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="B39" s="50" t="inlineStr">
-        <is>
-          <t>3 Bedroom</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E39" s="51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G39" s="52" t="inlineStr">
-        <is>
-          <t>3 Bedroom</t>
-        </is>
-      </c>
-      <c r="H39" s="32">
-        <f>IFERROR(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="I39" s="32">
-        <f>IFERROR(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J39" s="53">
-        <f>IFERROR(INDEX(Database!$AM:$AM,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1">
-      <c r="B40" s="54" t="inlineStr">
-        <is>
-          <t>Total / Blended</t>
-        </is>
-      </c>
-      <c r="C40" s="55">
-        <f>SUM(C36:C39)</f>
-        <v/>
-      </c>
-      <c r="D40" s="55">
-        <f>IFERROR(SUMPRODUCT(D36:D39,C36:C39)/C40,0)</f>
-        <v/>
-      </c>
-      <c r="E40" s="46">
-        <f>IFERROR(SUMPRODUCT(E36:E39,C36:C39)/C40,0)</f>
-        <v/>
-      </c>
-      <c r="G40" s="56" t="inlineStr">
-        <is>
-          <t>Total / Blended</t>
-        </is>
-      </c>
-      <c r="H40" s="57">
-        <f>SUM(H36:H39)</f>
-        <v/>
-      </c>
-      <c r="I40" s="57">
-        <f>IFERROR(SUMPRODUCT(I36:I39,H36:H39)/H40,0)</f>
-        <v/>
-      </c>
-      <c r="J40" s="48">
-        <f>IFERROR(SUMPRODUCT(J36:J39,H36:H39)/H40,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" outlineLevel="1"/>
-    <row r="42" outlineLevel="1">
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
-      <c r="E42" s="46">
-        <f>Blended_PUPM*Units_Total*12</f>
-        <v/>
-      </c>
-      <c r="G42" s="47" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
-      <c r="J42" s="48">
-        <f>Blended_PUPM_Cur*Units_Total_Cur*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" outlineLevel="1">
-      <c r="B43" s="29" t="inlineStr">
-        <is>
-          <t>Vacancy</t>
-        </is>
-      </c>
-      <c r="D43" s="43" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E43" s="58">
-        <f>-GPR_In*D43</f>
-        <v/>
-      </c>
-      <c r="G43" s="31" t="inlineStr">
-        <is>
-          <t>Vacancy</t>
-        </is>
-      </c>
-      <c r="I43" s="44">
-        <f>IFERROR(INDEX(Database!$AN:$AN,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J43" s="59">
-        <f>-GPR_Cur*I43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" outlineLevel="1">
-      <c r="B44" s="29" t="inlineStr">
-        <is>
-          <t>Concessions</t>
-        </is>
-      </c>
-      <c r="D44" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="58">
-        <f>-GPR_In*D44</f>
-        <v/>
-      </c>
-      <c r="G44" s="31" t="inlineStr">
-        <is>
-          <t>Concessions</t>
-        </is>
-      </c>
-      <c r="I44" s="44">
-        <f>IFERROR(INDEX(Database!$AO:$AO,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J44" s="59">
-        <f>-GPR_Cur*I44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" outlineLevel="1">
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="D45" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="58">
-        <f>-GPR_In*D45</f>
-        <v/>
-      </c>
-      <c r="G45" s="31" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="I45" s="44">
-        <f>IFERROR(INDEX(Database!$AP:$AP,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J45" s="59">
-        <f>-GPR_Cur*I45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" outlineLevel="1">
-      <c r="B46" s="29" t="inlineStr">
-        <is>
-          <t>Collection Loss</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="58">
-        <f>-GPR_In*D46</f>
-        <v/>
-      </c>
-      <c r="G46" s="31" t="inlineStr">
-        <is>
-          <t>Collection Loss</t>
-        </is>
-      </c>
-      <c r="I46" s="44">
-        <f>IFERROR(INDEX(Database!$AQ:$AQ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J46" s="59">
-        <f>-GPR_Cur*I46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" outlineLevel="1">
-      <c r="B47" s="45" t="inlineStr">
-        <is>
-          <t>Effective Rental Revenue</t>
-        </is>
-      </c>
-      <c r="E47" s="46">
-        <f>GPR_In+E43+E44+E45+E46</f>
-        <v/>
-      </c>
-      <c r="G47" s="47" t="inlineStr">
-        <is>
-          <t>Effective Rental Revenue</t>
-        </is>
-      </c>
-      <c r="J47" s="48">
-        <f>GPR_Cur+J43+J44+J45+J46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="26" t="inlineStr">
-        <is>
-          <t>Other Residential Income (Exhibit C)</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="28" t="inlineStr">
-        <is>
-          <t>Input  |  Current -&gt;</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n"/>
-      <c r="I48" s="27" t="n"/>
-      <c r="J48" s="27" t="n"/>
-    </row>
-    <row r="49" outlineLevel="1">
-      <c r="B49" s="49" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D49" s="49" t="inlineStr">
-        <is>
-          <t>$ PUPM</t>
-        </is>
-      </c>
-      <c r="E49" s="49" t="inlineStr">
-        <is>
-          <t>$ Annual</t>
-        </is>
-      </c>
-      <c r="G49" s="49" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I49" s="49" t="inlineStr">
-        <is>
-          <t>$ PUPM</t>
-        </is>
-      </c>
-      <c r="J49" s="49" t="inlineStr">
-        <is>
-          <t>$ Annual</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" outlineLevel="1">
-      <c r="B50" s="50" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="D50" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="E50" s="58">
-        <f>N(D50)*12*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G50" s="52" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="I50" s="42">
-        <f>IFERROR(INDEX(Database!$AS:$AS,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J50" s="53">
-        <f>N(I50)*12*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1">
-      <c r="B51" s="50" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="D51" s="41" t="inlineStr"/>
-      <c r="E51" s="58">
-        <f>N(D51)*12*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G51" s="52" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="I51" s="42">
-        <f>IFERROR(INDEX(Database!$AU:$AU,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J51" s="53">
-        <f>N(I51)*12*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" outlineLevel="1">
-      <c r="B52" s="50" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="D52" s="41" t="inlineStr"/>
-      <c r="E52" s="58">
-        <f>N(D52)*12*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G52" s="52" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="I52" s="42">
-        <f>IFERROR(INDEX(Database!$AW:$AW,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J52" s="53">
-        <f>N(I52)*12*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" outlineLevel="1">
-      <c r="B53" s="50" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="D53" s="41" t="inlineStr"/>
-      <c r="E53" s="58">
-        <f>N(D53)*12*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G53" s="52" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="I53" s="42">
-        <f>IFERROR(INDEX(Database!$AY:$AY,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J53" s="53">
-        <f>N(I53)*12*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" outlineLevel="1">
-      <c r="B54" s="50" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="D54" s="41" t="inlineStr"/>
-      <c r="E54" s="58">
-        <f>N(D54)*12*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G54" s="52" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="I54" s="42">
-        <f>IFERROR(INDEX(Database!$BA:$BA,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J54" s="53">
-        <f>N(I54)*12*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" outlineLevel="1">
-      <c r="B55" s="54" t="inlineStr">
-        <is>
-          <t>Total Other Income</t>
-        </is>
-      </c>
-      <c r="E55" s="46">
-        <f>SUM(E50:E54)</f>
-        <v/>
-      </c>
-      <c r="G55" s="56" t="inlineStr">
-        <is>
-          <t>Total Other Income</t>
-        </is>
-      </c>
-      <c r="J55" s="48">
-        <f>SUM(J50:J54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" outlineLevel="1"/>
-    <row r="57" outlineLevel="1">
-      <c r="B57" s="54" t="inlineStr">
-        <is>
-          <t>Effective Gross Revenue (EGR)</t>
-        </is>
-      </c>
-      <c r="E57" s="46">
-        <f>ERR_In+OtherInc_In</f>
-        <v/>
-      </c>
-      <c r="G57" s="56" t="inlineStr">
-        <is>
-          <t>Effective Gross Revenue (EGR)</t>
-        </is>
-      </c>
-      <c r="J57" s="48">
-        <f>ERR_Cur+OtherInc_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" outlineLevel="1"/>
-    <row r="59">
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>Multifamily Operating Expenses (Exhibit D)</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="n"/>
-      <c r="D59" s="27" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="28" t="inlineStr">
-        <is>
-          <t>Input  |  Current -&gt;</t>
-        </is>
-      </c>
-      <c r="H59" s="27" t="n"/>
-      <c r="I59" s="27" t="n"/>
-      <c r="J59" s="27" t="n"/>
-    </row>
-    <row r="60" outlineLevel="1">
-      <c r="B60" s="49" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D60" s="49" t="inlineStr">
-        <is>
-          <t>$ PUPA</t>
-        </is>
-      </c>
-      <c r="E60" s="49" t="inlineStr">
-        <is>
-          <t>$ Annual</t>
-        </is>
-      </c>
-      <c r="G60" s="49" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I60" s="49" t="inlineStr">
-        <is>
-          <t>$ PUPA</t>
-        </is>
-      </c>
-      <c r="J60" s="49" t="inlineStr">
-        <is>
-          <t>$ Annual</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" outlineLevel="1">
-      <c r="B61" s="29" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="D61" s="51" t="n">
-        <v>1150</v>
-      </c>
-      <c r="E61" s="58">
-        <f>N(D61)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G61" s="31" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="I61" s="53">
-        <f>IFERROR(INDEX(Database!$BB:$BB,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J61" s="59">
-        <f>N(I61)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" outlineLevel="1">
-      <c r="B62" s="29" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D62" s="51" t="n">
-        <v>350</v>
-      </c>
-      <c r="E62" s="58">
-        <f>N(D62)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G62" s="31" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="I62" s="53">
-        <f>IFERROR(INDEX(Database!$BC:$BC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J62" s="59">
-        <f>N(I62)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" outlineLevel="1">
-      <c r="B63" s="29" t="inlineStr">
-        <is>
-          <t>Administrative</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="n">
-        <v>350</v>
-      </c>
-      <c r="E63" s="58">
-        <f>N(D63)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G63" s="31" t="inlineStr">
-        <is>
-          <t>Administrative</t>
-        </is>
-      </c>
-      <c r="I63" s="53">
-        <f>IFERROR(INDEX(Database!$BD:$BD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J63" s="59">
-        <f>N(I63)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="B64" s="29" t="inlineStr">
-        <is>
-          <t>Professional Fees</t>
-        </is>
-      </c>
-      <c r="D64" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E64" s="58">
-        <f>N(D64)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G64" s="31" t="inlineStr">
-        <is>
-          <t>Professional Fees</t>
-        </is>
-      </c>
-      <c r="I64" s="53">
-        <f>IFERROR(INDEX(Database!$BE:$BE,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J64" s="59">
-        <f>N(I64)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" outlineLevel="1">
-      <c r="B65" s="29" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maint.</t>
-        </is>
-      </c>
-      <c r="D65" s="51" t="n">
-        <v>300</v>
-      </c>
-      <c r="E65" s="58">
-        <f>N(D65)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G65" s="31" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maint.</t>
-        </is>
-      </c>
-      <c r="I65" s="53">
-        <f>IFERROR(INDEX(Database!$BF:$BF,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J65" s="59">
-        <f>N(I65)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" outlineLevel="1">
-      <c r="B66" s="29" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D66" s="51" t="n">
-        <v>900</v>
-      </c>
-      <c r="E66" s="58">
-        <f>N(D66)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G66" s="31" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="I66" s="53">
-        <f>IFERROR(INDEX(Database!$BG:$BG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J66" s="59">
-        <f>N(I66)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="B67" s="29" t="inlineStr">
+      <c r="E71" s="60">
+        <f>N(D71)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G71" s="33" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D67" s="51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E67" s="58">
-        <f>N(D67)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G67" s="31" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="I67" s="53">
-        <f>IFERROR(INDEX(Database!$BH:$BH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J67" s="59">
-        <f>N(I67)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" outlineLevel="1">
-      <c r="B68" s="29" t="inlineStr">
+      <c r="I71" s="55">
+        <f>IFERROR(INDEX(Database!$BI:$BI,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J71" s="61">
+        <f>N(I71)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1">
+      <c r="B72" s="31" t="inlineStr">
         <is>
           <t>RE Taxes</t>
         </is>
       </c>
-      <c r="D68" s="51" t="n">
+      <c r="D72" s="53" t="n">
         <v>4500</v>
       </c>
-      <c r="E68" s="58">
-        <f>N(D68)*Units_Total</f>
-        <v/>
-      </c>
-      <c r="G68" s="31" t="inlineStr">
+      <c r="E72" s="60">
+        <f>N(D72)*Units_Total</f>
+        <v/>
+      </c>
+      <c r="G72" s="33" t="inlineStr">
         <is>
           <t>RE Taxes</t>
         </is>
       </c>
-      <c r="I68" s="53">
-        <f>IFERROR(INDEX(Database!$BI:$BI,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J68" s="59">
-        <f>N(I68)*Units_Total_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" outlineLevel="1">
-      <c r="B69" s="29" t="inlineStr">
+      <c r="I72" s="55">
+        <f>IFERROR(INDEX(Database!$BJ:$BJ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J72" s="61">
+        <f>N(I72)*Units_Total_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="B73" s="31" t="inlineStr">
         <is>
           <t>Management Fee (% of EGR)</t>
         </is>
       </c>
-      <c r="D69" s="43" t="n">
+      <c r="D73" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="E69" s="58">
-        <f>D69*EGR_In</f>
-        <v/>
-      </c>
-      <c r="G69" s="31" t="inlineStr">
+      <c r="E73" s="60">
+        <f>D73*EGR_In</f>
+        <v/>
+      </c>
+      <c r="G73" s="33" t="inlineStr">
         <is>
           <t>Management Fee (% of EGR)</t>
         </is>
       </c>
-      <c r="I69" s="44">
-        <f>IFERROR(INDEX(Database!$BJ:$BJ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J69" s="59">
-        <f>I69*EGR_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" outlineLevel="1">
-      <c r="B70" s="54" t="inlineStr">
+      <c r="I73" s="43">
+        <f>IFERROR(INDEX(Database!$BK:$BK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J73" s="61">
+        <f>I73*EGR_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" outlineLevel="1">
+      <c r="B74" s="56" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="E70" s="46">
-        <f>E61+E62+E63+E64+E65+E66+E67+E68+E69</f>
-        <v/>
-      </c>
-      <c r="G70" s="56" t="inlineStr">
+      <c r="E74" s="48">
+        <f>E65+E66+E67+E68+E69+E70+E71+E72+E73</f>
+        <v/>
+      </c>
+      <c r="G74" s="58" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="J70" s="48">
-        <f>J61+J62+J63+J64+J65+J66+J67+J68+J69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" outlineLevel="1"/>
-    <row r="72">
-      <c r="B72" s="26" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="C72" s="27" t="n"/>
-      <c r="D72" s="27" t="n"/>
-      <c r="E72" s="27" t="n"/>
-      <c r="F72" s="27" t="n"/>
-      <c r="G72" s="28" t="inlineStr">
-        <is>
-          <t>Input  |  Current -&gt;</t>
-        </is>
-      </c>
-      <c r="H72" s="27" t="n"/>
-      <c r="I72" s="27" t="n"/>
-      <c r="J72" s="27" t="n"/>
-    </row>
-    <row r="73" outlineLevel="1">
-      <c r="B73" s="54" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="E73" s="46">
-        <f>EGR_In-TotOpEx_In+CommNOI_In</f>
-        <v/>
-      </c>
-      <c r="G73" s="56" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="J73" s="48">
-        <f>EGR_Cur-TotOpEx_Cur+CommNOI_Cur</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>OpEx Ratio</t>
-        </is>
-      </c>
-      <c r="E74" s="60">
-        <f>IFERROR(TotOpEx_In/EGR_In,0)</f>
-        <v/>
-      </c>
-      <c r="G74" s="52" t="inlineStr">
-        <is>
-          <t>OpEx Ratio</t>
-        </is>
-      </c>
-      <c r="J74" s="61">
-        <f>IFERROR(TotOpEx_Cur/EGR_Cur,0)</f>
+      <c r="J74" s="50">
+        <f>J65+J66+J67+J68+J69+J70+J71+J72+J73</f>
         <v/>
       </c>
     </row>
     <row r="75" outlineLevel="1"/>
     <row r="76">
-      <c r="B76" s="26" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="n"/>
+      <c r="D76" s="21" t="n"/>
+      <c r="E76" s="21" t="n"/>
+      <c r="F76" s="21" t="n"/>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>Input  |  Current -&gt;</t>
+        </is>
+      </c>
+      <c r="H76" s="21" t="n"/>
+      <c r="I76" s="21" t="n"/>
+      <c r="J76" s="21" t="n"/>
+    </row>
+    <row r="77" outlineLevel="1">
+      <c r="B77" s="56" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="E77" s="48">
+        <f>EGR_In-TotOpEx_In+CommNOI_In</f>
+        <v/>
+      </c>
+      <c r="G77" s="58" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="J77" s="50">
+        <f>EGR_Cur-TotOpEx_Cur+CommNOI_Cur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>OpEx Ratio</t>
+        </is>
+      </c>
+      <c r="E78" s="62">
+        <f>IFERROR(TotOpEx_In/EGR_In,0)</f>
+        <v/>
+      </c>
+      <c r="G78" s="54" t="inlineStr">
+        <is>
+          <t>OpEx Ratio</t>
+        </is>
+      </c>
+      <c r="J78" s="63">
+        <f>IFERROR(TotOpEx_Cur/EGR_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1"/>
+    <row r="80">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>Development Budget / Capital Costs</t>
         </is>
       </c>
-      <c r="C76" s="27" t="n"/>
-      <c r="D76" s="27" t="n"/>
-      <c r="E76" s="27" t="n"/>
-      <c r="F76" s="27" t="n"/>
-      <c r="G76" s="28" t="inlineStr">
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="21" t="n"/>
+      <c r="E80" s="21" t="n"/>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="30" t="inlineStr">
         <is>
           <t>Input  |  Current -&gt;</t>
         </is>
       </c>
-      <c r="H76" s="27" t="n"/>
-      <c r="I76" s="27" t="n"/>
-      <c r="J76" s="27" t="n"/>
-    </row>
-    <row r="77" outlineLevel="1">
-      <c r="B77" s="49" t="inlineStr">
+      <c r="H80" s="21" t="n"/>
+      <c r="I80" s="21" t="n"/>
+      <c r="J80" s="21" t="n"/>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="B81" s="51" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="D77" s="49" t="inlineStr">
+      <c r="D81" s="51" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E77" s="49" t="inlineStr">
+      <c r="E81" s="51" t="inlineStr">
         <is>
           <t>$/Unit</t>
         </is>
       </c>
-      <c r="G77" s="49" t="inlineStr">
+      <c r="G81" s="51" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="I77" s="49" t="inlineStr">
+      <c r="I81" s="51" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="J77" s="49" t="inlineStr">
+      <c r="J81" s="51" t="inlineStr">
         <is>
           <t>$/Unit</t>
         </is>
       </c>
     </row>
-    <row r="78" outlineLevel="1">
-      <c r="B78" s="29" t="inlineStr">
+    <row r="82" outlineLevel="1">
+      <c r="B82" s="31" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="D78" s="51" t="n">
+      <c r="D82" s="53" t="n">
         <v>8000000</v>
       </c>
-      <c r="E78" s="58">
-        <f>IFERROR(D78/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
+      <c r="E82" s="60">
+        <f>IFERROR(D82/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G82" s="33" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="I78" s="53">
-        <f>IFERROR(INDEX(Database!$BK:$BK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J78" s="59">
-        <f>IFERROR(I78/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" outlineLevel="1">
-      <c r="B79" s="29" t="inlineStr">
+      <c r="I82" s="55">
+        <f>IFERROR(INDEX(Database!$BL:$BL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J82" s="61">
+        <f>IFERROR(I82/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1">
+      <c r="B83" s="31" t="inlineStr">
         <is>
           <t>Shell / Core</t>
         </is>
       </c>
-      <c r="D79" s="51" t="n">
+      <c r="D83" s="53" t="n">
         <v>28000000</v>
       </c>
-      <c r="E79" s="58">
-        <f>IFERROR(D79/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
+      <c r="E83" s="60">
+        <f>IFERROR(D83/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G83" s="33" t="inlineStr">
         <is>
           <t>Shell / Core</t>
         </is>
       </c>
-      <c r="I79" s="53">
-        <f>IFERROR(INDEX(Database!$BL:$BL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J79" s="59">
-        <f>IFERROR(I79/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" outlineLevel="1">
-      <c r="B80" s="29" t="inlineStr">
+      <c r="I83" s="55">
+        <f>IFERROR(INDEX(Database!$BM:$BM,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J83" s="61">
+        <f>IFERROR(I83/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" outlineLevel="1">
+      <c r="B84" s="31" t="inlineStr">
         <is>
           <t>Sitework</t>
         </is>
       </c>
-      <c r="D80" s="51" t="n">
+      <c r="D84" s="53" t="n">
         <v>4000000</v>
       </c>
-      <c r="E80" s="58">
-        <f>IFERROR(D80/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
+      <c r="E84" s="60">
+        <f>IFERROR(D84/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G84" s="33" t="inlineStr">
         <is>
           <t>Sitework</t>
         </is>
       </c>
-      <c r="I80" s="53">
-        <f>IFERROR(INDEX(Database!$BM:$BM,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J80" s="59">
-        <f>IFERROR(I80/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="B81" s="29" t="inlineStr">
+      <c r="I84" s="55">
+        <f>IFERROR(INDEX(Database!$BN:$BN,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J84" s="61">
+        <f>IFERROR(I84/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1">
+      <c r="B85" s="31" t="inlineStr">
         <is>
           <t>Parking Structure</t>
         </is>
       </c>
-      <c r="D81" s="51" t="n">
+      <c r="D85" s="53" t="n">
         <v>6000000</v>
       </c>
-      <c r="E81" s="58">
-        <f>IFERROR(D81/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
+      <c r="E85" s="60">
+        <f>IFERROR(D85/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G85" s="33" t="inlineStr">
         <is>
           <t>Parking Structure</t>
         </is>
       </c>
-      <c r="I81" s="53">
-        <f>IFERROR(INDEX(Database!$BN:$BN,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J81" s="59">
-        <f>IFERROR(I81/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="B82" s="29" t="inlineStr">
+      <c r="I85" s="55">
+        <f>IFERROR(INDEX(Database!$BO:$BO,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J85" s="61">
+        <f>IFERROR(I85/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" outlineLevel="1">
+      <c r="B86" s="31" t="inlineStr">
         <is>
           <t>FF&amp;E</t>
         </is>
       </c>
-      <c r="D82" s="51" t="n">
+      <c r="D86" s="53" t="n">
         <v>1500000</v>
       </c>
-      <c r="E82" s="58">
-        <f>IFERROR(D82/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
+      <c r="E86" s="60">
+        <f>IFERROR(D86/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G86" s="33" t="inlineStr">
         <is>
           <t>FF&amp;E</t>
         </is>
       </c>
-      <c r="I82" s="53">
-        <f>IFERROR(INDEX(Database!$BO:$BO,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J82" s="59">
-        <f>IFERROR(I82/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" outlineLevel="1">
-      <c r="B83" s="29" t="inlineStr">
+      <c r="I86" s="55">
+        <f>IFERROR(INDEX(Database!$BP:$BP,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J86" s="61">
+        <f>IFERROR(I86/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" outlineLevel="1">
+      <c r="B87" s="31" t="inlineStr">
         <is>
           <t>GC Fee</t>
         </is>
       </c>
-      <c r="D83" s="51" t="n">
+      <c r="D87" s="53" t="n">
         <v>2000000</v>
       </c>
-      <c r="E83" s="58">
-        <f>IFERROR(D83/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
+      <c r="E87" s="60">
+        <f>IFERROR(D87/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G87" s="33" t="inlineStr">
         <is>
           <t>GC Fee</t>
         </is>
       </c>
-      <c r="I83" s="53">
-        <f>IFERROR(INDEX(Database!$BP:$BP,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J83" s="59">
-        <f>IFERROR(I83/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" outlineLevel="1">
-      <c r="B84" s="29" t="inlineStr">
+      <c r="I87" s="55">
+        <f>IFERROR(INDEX(Database!$BQ:$BQ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J87" s="61">
+        <f>IFERROR(I87/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" outlineLevel="1">
+      <c r="B88" s="31" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="D84" s="51" t="n">
+      <c r="D88" s="53" t="n">
         <v>2500000</v>
       </c>
-      <c r="E84" s="58">
-        <f>IFERROR(D84/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G84" s="31" t="inlineStr">
+      <c r="E88" s="60">
+        <f>IFERROR(D88/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G88" s="33" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="I84" s="53">
-        <f>IFERROR(INDEX(Database!$BQ:$BQ,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J84" s="59">
-        <f>IFERROR(I84/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" outlineLevel="1">
-      <c r="B85" s="29" t="inlineStr">
+      <c r="I88" s="55">
+        <f>IFERROR(INDEX(Database!$BR:$BR,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J88" s="61">
+        <f>IFERROR(I88/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" outlineLevel="1">
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>Permits &amp; Impact Fees</t>
         </is>
       </c>
-      <c r="D85" s="51" t="n">
+      <c r="D89" s="53" t="n">
         <v>1800000</v>
       </c>
-      <c r="E85" s="58">
-        <f>IFERROR(D85/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G85" s="31" t="inlineStr">
+      <c r="E89" s="60">
+        <f>IFERROR(D89/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G89" s="33" t="inlineStr">
         <is>
           <t>Permits &amp; Impact Fees</t>
         </is>
       </c>
-      <c r="I85" s="53">
-        <f>IFERROR(INDEX(Database!$BR:$BR,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J85" s="59">
-        <f>IFERROR(I85/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" outlineLevel="1">
-      <c r="B86" s="29" t="inlineStr">
+      <c r="I89" s="55">
+        <f>IFERROR(INDEX(Database!$BS:$BS,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J89" s="61">
+        <f>IFERROR(I89/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" outlineLevel="1">
+      <c r="B90" s="31" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D86" s="51" t="n">
+      <c r="D90" s="53" t="n">
         <v>600000</v>
       </c>
-      <c r="E86" s="58">
-        <f>IFERROR(D86/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G86" s="31" t="inlineStr">
+      <c r="E90" s="60">
+        <f>IFERROR(D90/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G90" s="33" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="I86" s="53">
-        <f>IFERROR(INDEX(Database!$BS:$BS,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J86" s="59">
-        <f>IFERROR(I86/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" outlineLevel="1">
-      <c r="B87" s="29" t="inlineStr">
+      <c r="I90" s="55">
+        <f>IFERROR(INDEX(Database!$BT:$BT,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J90" s="61">
+        <f>IFERROR(I90/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" outlineLevel="1">
+      <c r="B91" s="31" t="inlineStr">
         <is>
           <t>Marketing / Lease-up</t>
         </is>
       </c>
-      <c r="D87" s="51" t="n">
+      <c r="D91" s="53" t="n">
         <v>700000</v>
       </c>
-      <c r="E87" s="58">
-        <f>IFERROR(D87/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G87" s="31" t="inlineStr">
+      <c r="E91" s="60">
+        <f>IFERROR(D91/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G91" s="33" t="inlineStr">
         <is>
           <t>Marketing / Lease-up</t>
         </is>
       </c>
-      <c r="I87" s="53">
-        <f>IFERROR(INDEX(Database!$BT:$BT,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J87" s="59">
-        <f>IFERROR(I87/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" outlineLevel="1">
-      <c r="B88" s="29" t="inlineStr">
+      <c r="I91" s="55">
+        <f>IFERROR(INDEX(Database!$BU:$BU,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J91" s="61">
+        <f>IFERROR(I91/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" outlineLevel="1">
+      <c r="B92" s="31" t="inlineStr">
         <is>
           <t>Developer Fee</t>
         </is>
       </c>
-      <c r="D88" s="51" t="n">
+      <c r="D92" s="53" t="n">
         <v>3000000</v>
       </c>
-      <c r="E88" s="58">
-        <f>IFERROR(D88/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G88" s="31" t="inlineStr">
+      <c r="E92" s="60">
+        <f>IFERROR(D92/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G92" s="33" t="inlineStr">
         <is>
           <t>Developer Fee</t>
         </is>
       </c>
-      <c r="I88" s="53">
-        <f>IFERROR(INDEX(Database!$BU:$BU,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J88" s="59">
-        <f>IFERROR(I88/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" outlineLevel="1">
-      <c r="B89" s="29" t="inlineStr">
+      <c r="I92" s="55">
+        <f>IFERROR(INDEX(Database!$BV:$BV,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J92" s="61">
+        <f>IFERROR(I92/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1">
+      <c r="B93" s="31" t="inlineStr">
         <is>
           <t>Taxes &amp; Insurance (Constr.)</t>
         </is>
       </c>
-      <c r="D89" s="51" t="n">
+      <c r="D93" s="53" t="n">
         <v>900000</v>
       </c>
-      <c r="E89" s="58">
-        <f>IFERROR(D89/Units_Total,0)</f>
-        <v/>
-      </c>
-      <c r="G89" s="31" t="inlineStr">
+      <c r="E93" s="60">
+        <f>IFERROR(D93/Units_Total,0)</f>
+        <v/>
+      </c>
+      <c r="G93" s="33" t="inlineStr">
         <is>
           <t>Taxes &amp; Insurance (Constr.)</t>
         </is>
       </c>
-      <c r="I89" s="53">
-        <f>IFERROR(INDEX(Database!$BV:$BV,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
-        <v/>
-      </c>
-      <c r="J89" s="59">
-        <f>IFERROR(I89/Units_Total_Cur,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" outlineLevel="1">
-      <c r="B90" s="54" t="inlineStr">
+      <c r="I93" s="55">
+        <f>IFERROR(INDEX(Database!$BW:$BW,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,SelectedProject),Database!$A:$A,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="J93" s="61">
+        <f>IFERROR(I93/Units_Total_Cur,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1">
+      <c r="B94" s="56" t="inlineStr">
         <is>
           <t>Total Development Cost</t>
         </is>
       </c>
-      <c r="E90" s="46">
-        <f>D78+D79+D80+D81+D82+D83+D84+D85+D86+D87+D88+D89</f>
-        <v/>
-      </c>
-      <c r="G90" s="56" t="inlineStr">
+      <c r="E94" s="48">
+        <f>D82+D83+D84+D85+D86+D87+D88+D89+D90+D91+D92+D93</f>
+        <v/>
+      </c>
+      <c r="G94" s="58" t="inlineStr">
         <is>
           <t>Total Development Cost</t>
         </is>
       </c>
-      <c r="J90" s="48">
-        <f>I78+I79+I80+I81+I82+I83+I84+I85+I86+I87+I88+I89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" outlineLevel="1"/>
+      <c r="J94" s="50">
+        <f>I82+I83+I84+I85+I86+I87+I88+I89+I90+I91+I92+I93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D15">
+  <conditionalFormatting sqref="D18">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISBLANK(D15)</formula>
+      <formula>ISBLANK(D18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
+  <conditionalFormatting sqref="D20">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISBLANK(D17)</formula>
+      <formula>ISBLANK(D20)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18">
+  <conditionalFormatting sqref="D21">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>ISBLANK(D18)</formula>
+      <formula>ISBLANK(D21)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=Project_List</formula1>
     </dataValidation>
-    <dataValidation sqref="D26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=YesNo_List</formula1>
     </dataValidation>
-    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=UnitType_List</formula1>
     </dataValidation>
-    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=UnitType_List</formula1>
     </dataValidation>
-    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=UnitType_List</formula1>
     </dataValidation>
-    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=UnitType_List</formula1>
     </dataValidation>
   </dataValidations>
@@ -3200,158 +3328,158 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>MASTER ASSUMPTIONS  -  program-wide growth defaults (Exhibit E)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Per-phase overrides live on the Console. Year 5 = Year 5+.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="D4" s="65" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E4" s="65" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="F4" s="65" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Market Rents</t>
         </is>
       </c>
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="D5" s="43" t="n">
+      <c r="D5" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="E5" s="43" t="n">
+      <c r="E5" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="F5" s="43" t="n">
+      <c r="F5" s="42" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>Affordable Rents</t>
         </is>
       </c>
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="F6" s="43" t="n">
+      <c r="F6" s="42" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>Retail Rents</t>
         </is>
       </c>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="42" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B8" s="43" t="n">
+      <c r="B8" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="42" t="n">
         <v>0.025</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="42" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="42" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="42" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3367,14 +3495,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>DATABASE  -  relational system of record (one row = one published record). Do not edit by hand.</t>
         </is>
@@ -3386,7 +3514,7 @@
           <t>MaxRecordsPerProject</t>
         </is>
       </c>
-      <c r="B2" s="68" t="n">
+      <c r="B2" s="70" t="n">
         <v>20</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -3396,868 +3524,879 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="69" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>RecordID</t>
         </is>
       </c>
-      <c r="B4" s="69" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C4" s="69" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="69" t="inlineStr">
+      <c r="D4" s="71" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="E4" s="69" t="inlineStr">
+      <c r="E4" s="71" t="inlineStr">
         <is>
           <t>UpdatedBy</t>
         </is>
       </c>
-      <c r="F4" s="69" t="inlineStr">
+      <c r="F4" s="71" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="G4" s="69" t="inlineStr">
+      <c r="G4" s="71" t="inlineStr">
         <is>
           <t>PhaseNo</t>
         </is>
       </c>
-      <c r="H4" s="69" t="inlineStr">
+      <c r="H4" s="71" t="inlineStr">
         <is>
           <t>ProjectName</t>
         </is>
       </c>
-      <c r="I4" s="69" t="inlineStr">
+      <c r="I4" s="71" t="inlineStr">
         <is>
           <t>LandAcres</t>
         </is>
       </c>
-      <c r="J4" s="69" t="inlineStr">
+      <c r="J4" s="71" t="inlineStr">
         <is>
           <t>ClosingDate</t>
         </is>
       </c>
-      <c r="K4" s="69" t="inlineStr">
+      <c r="K4" s="71" t="inlineStr">
         <is>
           <t>GSF</t>
         </is>
       </c>
-      <c r="L4" s="69" t="inlineStr">
+      <c r="L4" s="71" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="M4" s="69" t="inlineStr">
+      <c r="M4" s="71" t="inlineStr">
+        <is>
+          <t>ExitCapRate</t>
+        </is>
+      </c>
+      <c r="N4" s="71" t="inlineStr">
         <is>
           <t>off_ConstStart</t>
         </is>
       </c>
-      <c r="N4" s="69" t="inlineStr">
+      <c r="O4" s="71" t="inlineStr">
         <is>
           <t>off_InitOcc</t>
         </is>
       </c>
-      <c r="O4" s="69" t="inlineStr">
+      <c r="P4" s="71" t="inlineStr">
         <is>
           <t>off_ConstEnd</t>
         </is>
       </c>
-      <c r="P4" s="69" t="inlineStr">
+      <c r="Q4" s="71" t="inlineStr">
         <is>
           <t>off_Stab</t>
         </is>
       </c>
-      <c r="Q4" s="69" t="inlineStr">
+      <c r="R4" s="71" t="inlineStr">
         <is>
           <t>HasCommercial</t>
         </is>
       </c>
-      <c r="R4" s="69" t="inlineStr">
+      <c r="S4" s="71" t="inlineStr">
         <is>
           <t>CommSF</t>
         </is>
       </c>
-      <c r="S4" s="69" t="inlineStr">
+      <c r="T4" s="71" t="inlineStr">
         <is>
           <t>CommRentPSF</t>
         </is>
       </c>
-      <c r="T4" s="69" t="inlineStr">
+      <c r="U4" s="71" t="inlineStr">
         <is>
           <t>CommEscalation</t>
         </is>
       </c>
-      <c r="U4" s="69" t="inlineStr">
+      <c r="V4" s="71" t="inlineStr">
         <is>
           <t>CommAbatement</t>
         </is>
       </c>
-      <c r="V4" s="69" t="inlineStr">
+      <c r="W4" s="71" t="inlineStr">
         <is>
           <t>CommVacancy</t>
         </is>
       </c>
-      <c r="W4" s="69" t="inlineStr">
+      <c r="X4" s="71" t="inlineStr">
         <is>
           <t>CommOpExPSF</t>
         </is>
       </c>
-      <c r="X4" s="69" t="inlineStr">
+      <c r="Y4" s="71" t="inlineStr">
         <is>
           <t>UM1_Type</t>
         </is>
       </c>
-      <c r="Y4" s="69" t="inlineStr">
+      <c r="Z4" s="71" t="inlineStr">
         <is>
           <t>UM1_Count</t>
         </is>
       </c>
-      <c r="Z4" s="69" t="inlineStr">
+      <c r="AA4" s="71" t="inlineStr">
         <is>
           <t>UM1_AvgSF</t>
         </is>
       </c>
-      <c r="AA4" s="69" t="inlineStr">
+      <c r="AB4" s="71" t="inlineStr">
         <is>
           <t>UM1_PUPM</t>
         </is>
       </c>
-      <c r="AB4" s="69" t="inlineStr">
+      <c r="AC4" s="71" t="inlineStr">
         <is>
           <t>UM2_Type</t>
         </is>
       </c>
-      <c r="AC4" s="69" t="inlineStr">
+      <c r="AD4" s="71" t="inlineStr">
         <is>
           <t>UM2_Count</t>
         </is>
       </c>
-      <c r="AD4" s="69" t="inlineStr">
+      <c r="AE4" s="71" t="inlineStr">
         <is>
           <t>UM2_AvgSF</t>
         </is>
       </c>
-      <c r="AE4" s="69" t="inlineStr">
+      <c r="AF4" s="71" t="inlineStr">
         <is>
           <t>UM2_PUPM</t>
         </is>
       </c>
-      <c r="AF4" s="69" t="inlineStr">
+      <c r="AG4" s="71" t="inlineStr">
         <is>
           <t>UM3_Type</t>
         </is>
       </c>
-      <c r="AG4" s="69" t="inlineStr">
+      <c r="AH4" s="71" t="inlineStr">
         <is>
           <t>UM3_Count</t>
         </is>
       </c>
-      <c r="AH4" s="69" t="inlineStr">
+      <c r="AI4" s="71" t="inlineStr">
         <is>
           <t>UM3_AvgSF</t>
         </is>
       </c>
-      <c r="AI4" s="69" t="inlineStr">
+      <c r="AJ4" s="71" t="inlineStr">
         <is>
           <t>UM3_PUPM</t>
         </is>
       </c>
-      <c r="AJ4" s="69" t="inlineStr">
+      <c r="AK4" s="71" t="inlineStr">
         <is>
           <t>UM4_Type</t>
         </is>
       </c>
-      <c r="AK4" s="69" t="inlineStr">
+      <c r="AL4" s="71" t="inlineStr">
         <is>
           <t>UM4_Count</t>
         </is>
       </c>
-      <c r="AL4" s="69" t="inlineStr">
+      <c r="AM4" s="71" t="inlineStr">
         <is>
           <t>UM4_AvgSF</t>
         </is>
       </c>
-      <c r="AM4" s="69" t="inlineStr">
+      <c r="AN4" s="71" t="inlineStr">
         <is>
           <t>UM4_PUPM</t>
         </is>
       </c>
-      <c r="AN4" s="69" t="inlineStr">
+      <c r="AO4" s="71" t="inlineStr">
         <is>
           <t>ResVacancy</t>
         </is>
       </c>
-      <c r="AO4" s="69" t="inlineStr">
+      <c r="AP4" s="71" t="inlineStr">
         <is>
           <t>ResConcessions</t>
         </is>
       </c>
-      <c r="AP4" s="69" t="inlineStr">
+      <c r="AQ4" s="71" t="inlineStr">
         <is>
           <t>ResModel</t>
         </is>
       </c>
-      <c r="AQ4" s="69" t="inlineStr">
+      <c r="AR4" s="71" t="inlineStr">
         <is>
           <t>ResCollLoss</t>
         </is>
       </c>
-      <c r="AR4" s="69" t="inlineStr">
+      <c r="AS4" s="71" t="inlineStr">
         <is>
           <t>OI1_Name</t>
         </is>
       </c>
-      <c r="AS4" s="69" t="inlineStr">
+      <c r="AT4" s="71" t="inlineStr">
         <is>
           <t>OI1_PUPM</t>
         </is>
       </c>
-      <c r="AT4" s="69" t="inlineStr">
+      <c r="AU4" s="71" t="inlineStr">
         <is>
           <t>OI2_Name</t>
         </is>
       </c>
-      <c r="AU4" s="69" t="inlineStr">
+      <c r="AV4" s="71" t="inlineStr">
         <is>
           <t>OI2_PUPM</t>
         </is>
       </c>
-      <c r="AV4" s="69" t="inlineStr">
+      <c r="AW4" s="71" t="inlineStr">
         <is>
           <t>OI3_Name</t>
         </is>
       </c>
-      <c r="AW4" s="69" t="inlineStr">
+      <c r="AX4" s="71" t="inlineStr">
         <is>
           <t>OI3_PUPM</t>
         </is>
       </c>
-      <c r="AX4" s="69" t="inlineStr">
+      <c r="AY4" s="71" t="inlineStr">
         <is>
           <t>OI4_Name</t>
         </is>
       </c>
-      <c r="AY4" s="69" t="inlineStr">
+      <c r="AZ4" s="71" t="inlineStr">
         <is>
           <t>OI4_PUPM</t>
         </is>
       </c>
-      <c r="AZ4" s="69" t="inlineStr">
+      <c r="BA4" s="71" t="inlineStr">
         <is>
           <t>OI5_Name</t>
         </is>
       </c>
-      <c r="BA4" s="69" t="inlineStr">
+      <c r="BB4" s="71" t="inlineStr">
         <is>
           <t>OI5_PUPM</t>
         </is>
       </c>
-      <c r="BB4" s="69" t="inlineStr">
+      <c r="BC4" s="71" t="inlineStr">
         <is>
           <t>OpEx_Payroll</t>
         </is>
       </c>
-      <c r="BC4" s="69" t="inlineStr">
+      <c r="BD4" s="71" t="inlineStr">
         <is>
           <t>OpEx_Marketing</t>
         </is>
       </c>
-      <c r="BD4" s="69" t="inlineStr">
+      <c r="BE4" s="71" t="inlineStr">
         <is>
           <t>OpEx_Admin</t>
         </is>
       </c>
-      <c r="BE4" s="69" t="inlineStr">
+      <c r="BF4" s="71" t="inlineStr">
         <is>
           <t>OpEx_ProfFees</t>
         </is>
       </c>
-      <c r="BF4" s="69" t="inlineStr">
+      <c r="BG4" s="71" t="inlineStr">
         <is>
           <t>OpEx_RM</t>
         </is>
       </c>
-      <c r="BG4" s="69" t="inlineStr">
+      <c r="BH4" s="71" t="inlineStr">
         <is>
           <t>OpEx_Utilities</t>
         </is>
       </c>
-      <c r="BH4" s="69" t="inlineStr">
+      <c r="BI4" s="71" t="inlineStr">
         <is>
           <t>OpEx_Insurance</t>
         </is>
       </c>
-      <c r="BI4" s="69" t="inlineStr">
+      <c r="BJ4" s="71" t="inlineStr">
         <is>
           <t>OpEx_RETaxes</t>
         </is>
       </c>
-      <c r="BJ4" s="69" t="inlineStr">
+      <c r="BK4" s="71" t="inlineStr">
         <is>
           <t>OpEx_MgmtFeePct</t>
         </is>
       </c>
-      <c r="BK4" s="69" t="inlineStr">
+      <c r="BL4" s="71" t="inlineStr">
         <is>
           <t>Bud_Land</t>
         </is>
       </c>
-      <c r="BL4" s="69" t="inlineStr">
+      <c r="BM4" s="71" t="inlineStr">
         <is>
           <t>Bud_Shell</t>
         </is>
       </c>
-      <c r="BM4" s="69" t="inlineStr">
+      <c r="BN4" s="71" t="inlineStr">
         <is>
           <t>Bud_Sitework</t>
         </is>
       </c>
-      <c r="BN4" s="69" t="inlineStr">
+      <c r="BO4" s="71" t="inlineStr">
         <is>
           <t>Bud_Parking</t>
         </is>
       </c>
-      <c r="BO4" s="69" t="inlineStr">
+      <c r="BP4" s="71" t="inlineStr">
         <is>
           <t>Bud_FFE</t>
         </is>
       </c>
-      <c r="BP4" s="69" t="inlineStr">
+      <c r="BQ4" s="71" t="inlineStr">
         <is>
           <t>Bud_GCFee</t>
         </is>
       </c>
-      <c r="BQ4" s="69" t="inlineStr">
+      <c r="BR4" s="71" t="inlineStr">
         <is>
           <t>Bud_AE</t>
         </is>
       </c>
-      <c r="BR4" s="69" t="inlineStr">
+      <c r="BS4" s="71" t="inlineStr">
         <is>
           <t>Bud_Permits</t>
         </is>
       </c>
-      <c r="BS4" s="69" t="inlineStr">
+      <c r="BT4" s="71" t="inlineStr">
         <is>
           <t>Bud_Legal</t>
         </is>
       </c>
-      <c r="BT4" s="69" t="inlineStr">
+      <c r="BU4" s="71" t="inlineStr">
         <is>
           <t>Bud_Mktg</t>
         </is>
       </c>
-      <c r="BU4" s="69" t="inlineStr">
+      <c r="BV4" s="71" t="inlineStr">
         <is>
           <t>Bud_DevFee</t>
         </is>
       </c>
-      <c r="BV4" s="69" t="inlineStr">
+      <c r="BW4" s="71" t="inlineStr">
         <is>
           <t>Bud_TaxIns</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="70" t="n">
+      <c r="A5" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>RAD 1</t>
         </is>
       </c>
-      <c r="C5" s="70" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="D5" s="71" t="n">
+      <c r="D5" s="73" t="n">
         <v>46196</v>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="F5" s="70" t="inlineStr">
+      <c r="F5" s="72" t="inlineStr">
         <is>
           <t>initial seed record</t>
         </is>
       </c>
-      <c r="G5" s="70">
-        <f>Cockpit!$D$14</f>
-        <v/>
-      </c>
-      <c r="H5" s="70">
-        <f>Cockpit!$D$15</f>
-        <v/>
-      </c>
-      <c r="I5" s="70">
-        <f>Cockpit!$D$16</f>
-        <v/>
-      </c>
-      <c r="J5" s="70">
+      <c r="G5" s="72">
         <f>Cockpit!$D$17</f>
         <v/>
       </c>
-      <c r="K5" s="70">
+      <c r="H5" s="72">
         <f>Cockpit!$D$18</f>
         <v/>
       </c>
-      <c r="L5" s="70">
+      <c r="I5" s="72">
         <f>Cockpit!$D$19</f>
         <v/>
       </c>
-      <c r="M5" s="70">
+      <c r="J5" s="72">
+        <f>Cockpit!$D$20</f>
+        <v/>
+      </c>
+      <c r="K5" s="72">
         <f>Cockpit!$D$21</f>
         <v/>
       </c>
-      <c r="N5" s="70">
+      <c r="L5" s="72">
         <f>Cockpit!$D$22</f>
         <v/>
       </c>
-      <c r="O5" s="70">
+      <c r="M5" s="72">
         <f>Cockpit!$D$23</f>
         <v/>
       </c>
-      <c r="P5" s="70">
-        <f>Cockpit!$D$24</f>
-        <v/>
-      </c>
-      <c r="Q5" s="70">
+      <c r="N5" s="72">
+        <f>Cockpit!$D$25</f>
+        <v/>
+      </c>
+      <c r="O5" s="72">
         <f>Cockpit!$D$26</f>
         <v/>
       </c>
-      <c r="R5" s="70">
+      <c r="P5" s="72">
         <f>Cockpit!$D$27</f>
         <v/>
       </c>
-      <c r="S5" s="70">
+      <c r="Q5" s="72">
         <f>Cockpit!$D$28</f>
         <v/>
       </c>
-      <c r="T5" s="70">
-        <f>Cockpit!$D$29</f>
-        <v/>
-      </c>
-      <c r="U5" s="70">
+      <c r="R5" s="72">
         <f>Cockpit!$D$30</f>
         <v/>
       </c>
-      <c r="V5" s="70">
+      <c r="S5" s="72">
         <f>Cockpit!$D$31</f>
         <v/>
       </c>
-      <c r="W5" s="70">
+      <c r="T5" s="72">
         <f>Cockpit!$D$32</f>
         <v/>
       </c>
-      <c r="X5" s="70">
-        <f>Cockpit!$B$36</f>
-        <v/>
-      </c>
-      <c r="Y5" s="70">
-        <f>Cockpit!$C$36</f>
-        <v/>
-      </c>
-      <c r="Z5" s="70">
+      <c r="U5" s="72">
+        <f>Cockpit!$D$33</f>
+        <v/>
+      </c>
+      <c r="V5" s="72">
+        <f>Cockpit!$D$34</f>
+        <v/>
+      </c>
+      <c r="W5" s="72">
+        <f>Cockpit!$D$35</f>
+        <v/>
+      </c>
+      <c r="X5" s="72">
         <f>Cockpit!$D$36</f>
         <v/>
       </c>
-      <c r="AA5" s="70">
-        <f>Cockpit!$E$36</f>
-        <v/>
-      </c>
-      <c r="AB5" s="70">
-        <f>Cockpit!$B$37</f>
-        <v/>
-      </c>
-      <c r="AC5" s="70">
-        <f>Cockpit!$C$37</f>
-        <v/>
-      </c>
-      <c r="AD5" s="70">
-        <f>Cockpit!$D$37</f>
-        <v/>
-      </c>
-      <c r="AE5" s="70">
-        <f>Cockpit!$E$37</f>
-        <v/>
-      </c>
-      <c r="AF5" s="70">
-        <f>Cockpit!$B$38</f>
-        <v/>
-      </c>
-      <c r="AG5" s="70">
-        <f>Cockpit!$C$38</f>
-        <v/>
-      </c>
-      <c r="AH5" s="70">
-        <f>Cockpit!$D$38</f>
-        <v/>
-      </c>
-      <c r="AI5" s="70">
-        <f>Cockpit!$E$38</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="70">
-        <f>Cockpit!$B$39</f>
-        <v/>
-      </c>
-      <c r="AK5" s="70">
-        <f>Cockpit!$C$39</f>
-        <v/>
-      </c>
-      <c r="AL5" s="70">
-        <f>Cockpit!$D$39</f>
-        <v/>
-      </c>
-      <c r="AM5" s="70">
-        <f>Cockpit!$E$39</f>
-        <v/>
-      </c>
-      <c r="AN5" s="70">
+      <c r="Y5" s="72">
+        <f>Cockpit!$B$40</f>
+        <v/>
+      </c>
+      <c r="Z5" s="72">
+        <f>Cockpit!$C$40</f>
+        <v/>
+      </c>
+      <c r="AA5" s="72">
+        <f>Cockpit!$D$40</f>
+        <v/>
+      </c>
+      <c r="AB5" s="72">
+        <f>Cockpit!$E$40</f>
+        <v/>
+      </c>
+      <c r="AC5" s="72">
+        <f>Cockpit!$B$41</f>
+        <v/>
+      </c>
+      <c r="AD5" s="72">
+        <f>Cockpit!$C$41</f>
+        <v/>
+      </c>
+      <c r="AE5" s="72">
+        <f>Cockpit!$D$41</f>
+        <v/>
+      </c>
+      <c r="AF5" s="72">
+        <f>Cockpit!$E$41</f>
+        <v/>
+      </c>
+      <c r="AG5" s="72">
+        <f>Cockpit!$B$42</f>
+        <v/>
+      </c>
+      <c r="AH5" s="72">
+        <f>Cockpit!$C$42</f>
+        <v/>
+      </c>
+      <c r="AI5" s="72">
+        <f>Cockpit!$D$42</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="72">
+        <f>Cockpit!$E$42</f>
+        <v/>
+      </c>
+      <c r="AK5" s="72">
+        <f>Cockpit!$B$43</f>
+        <v/>
+      </c>
+      <c r="AL5" s="72">
+        <f>Cockpit!$C$43</f>
+        <v/>
+      </c>
+      <c r="AM5" s="72">
         <f>Cockpit!$D$43</f>
         <v/>
       </c>
-      <c r="AO5" s="70">
-        <f>Cockpit!$D$44</f>
-        <v/>
-      </c>
-      <c r="AP5" s="70">
-        <f>Cockpit!$D$45</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="70">
-        <f>Cockpit!$D$46</f>
-        <v/>
-      </c>
-      <c r="AR5" s="70">
-        <f>Cockpit!$B$50</f>
-        <v/>
-      </c>
-      <c r="AS5" s="70">
+      <c r="AN5" s="72">
+        <f>Cockpit!$E$43</f>
+        <v/>
+      </c>
+      <c r="AO5" s="72">
+        <f>Cockpit!$D$47</f>
+        <v/>
+      </c>
+      <c r="AP5" s="72">
+        <f>Cockpit!$D$48</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="72">
+        <f>Cockpit!$D$49</f>
+        <v/>
+      </c>
+      <c r="AR5" s="72">
         <f>Cockpit!$D$50</f>
         <v/>
       </c>
-      <c r="AT5" s="70">
-        <f>Cockpit!$B$51</f>
-        <v/>
-      </c>
-      <c r="AU5" s="70">
-        <f>Cockpit!$D$51</f>
-        <v/>
-      </c>
-      <c r="AV5" s="70">
-        <f>Cockpit!$B$52</f>
-        <v/>
-      </c>
-      <c r="AW5" s="70">
-        <f>Cockpit!$D$52</f>
-        <v/>
-      </c>
-      <c r="AX5" s="70">
-        <f>Cockpit!$B$53</f>
-        <v/>
-      </c>
-      <c r="AY5" s="70">
-        <f>Cockpit!$D$53</f>
-        <v/>
-      </c>
-      <c r="AZ5" s="70">
+      <c r="AS5" s="72">
         <f>Cockpit!$B$54</f>
         <v/>
       </c>
-      <c r="BA5" s="70">
+      <c r="AT5" s="72">
         <f>Cockpit!$D$54</f>
         <v/>
       </c>
-      <c r="BB5" s="70">
-        <f>Cockpit!$D$61</f>
-        <v/>
-      </c>
-      <c r="BC5" s="70">
-        <f>Cockpit!$D$62</f>
-        <v/>
-      </c>
-      <c r="BD5" s="70">
-        <f>Cockpit!$D$63</f>
-        <v/>
-      </c>
-      <c r="BE5" s="70">
-        <f>Cockpit!$D$64</f>
-        <v/>
-      </c>
-      <c r="BF5" s="70">
+      <c r="AU5" s="72">
+        <f>Cockpit!$B$55</f>
+        <v/>
+      </c>
+      <c r="AV5" s="72">
+        <f>Cockpit!$D$55</f>
+        <v/>
+      </c>
+      <c r="AW5" s="72">
+        <f>Cockpit!$B$56</f>
+        <v/>
+      </c>
+      <c r="AX5" s="72">
+        <f>Cockpit!$D$56</f>
+        <v/>
+      </c>
+      <c r="AY5" s="72">
+        <f>Cockpit!$B$57</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="72">
+        <f>Cockpit!$D$57</f>
+        <v/>
+      </c>
+      <c r="BA5" s="72">
+        <f>Cockpit!$B$58</f>
+        <v/>
+      </c>
+      <c r="BB5" s="72">
+        <f>Cockpit!$D$58</f>
+        <v/>
+      </c>
+      <c r="BC5" s="72">
         <f>Cockpit!$D$65</f>
         <v/>
       </c>
-      <c r="BG5" s="70">
+      <c r="BD5" s="72">
         <f>Cockpit!$D$66</f>
         <v/>
       </c>
-      <c r="BH5" s="70">
+      <c r="BE5" s="72">
         <f>Cockpit!$D$67</f>
         <v/>
       </c>
-      <c r="BI5" s="70">
+      <c r="BF5" s="72">
         <f>Cockpit!$D$68</f>
         <v/>
       </c>
-      <c r="BJ5" s="70">
+      <c r="BG5" s="72">
         <f>Cockpit!$D$69</f>
         <v/>
       </c>
-      <c r="BK5" s="70">
-        <f>Cockpit!$D$78</f>
-        <v/>
-      </c>
-      <c r="BL5" s="70">
-        <f>Cockpit!$D$79</f>
-        <v/>
-      </c>
-      <c r="BM5" s="70">
-        <f>Cockpit!$D$80</f>
-        <v/>
-      </c>
-      <c r="BN5" s="70">
-        <f>Cockpit!$D$81</f>
-        <v/>
-      </c>
-      <c r="BO5" s="70">
+      <c r="BH5" s="72">
+        <f>Cockpit!$D$70</f>
+        <v/>
+      </c>
+      <c r="BI5" s="72">
+        <f>Cockpit!$D$71</f>
+        <v/>
+      </c>
+      <c r="BJ5" s="72">
+        <f>Cockpit!$D$72</f>
+        <v/>
+      </c>
+      <c r="BK5" s="72">
+        <f>Cockpit!$D$73</f>
+        <v/>
+      </c>
+      <c r="BL5" s="72">
         <f>Cockpit!$D$82</f>
         <v/>
       </c>
-      <c r="BP5" s="70">
+      <c r="BM5" s="72">
         <f>Cockpit!$D$83</f>
         <v/>
       </c>
-      <c r="BQ5" s="70">
+      <c r="BN5" s="72">
         <f>Cockpit!$D$84</f>
         <v/>
       </c>
-      <c r="BR5" s="70">
+      <c r="BO5" s="72">
         <f>Cockpit!$D$85</f>
         <v/>
       </c>
-      <c r="BS5" s="70">
+      <c r="BP5" s="72">
         <f>Cockpit!$D$86</f>
         <v/>
       </c>
-      <c r="BT5" s="70">
+      <c r="BQ5" s="72">
         <f>Cockpit!$D$87</f>
         <v/>
       </c>
-      <c r="BU5" s="70">
+      <c r="BR5" s="72">
         <f>Cockpit!$D$88</f>
         <v/>
       </c>
-      <c r="BV5" s="70">
+      <c r="BS5" s="72">
         <f>Cockpit!$D$89</f>
         <v/>
       </c>
+      <c r="BT5" s="72">
+        <f>Cockpit!$D$90</f>
+        <v/>
+      </c>
+      <c r="BU5" s="72">
+        <f>Cockpit!$D$91</f>
+        <v/>
+      </c>
+      <c r="BV5" s="72">
+        <f>Cockpit!$D$92</f>
+        <v/>
+      </c>
+      <c r="BW5" s="72">
+        <f>Cockpit!$D$93</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="70" t="n">
+      <c r="A6" s="72" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>RAD 2</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="D6" s="71" t="n">
+      <c r="D6" s="73" t="n">
         <v>46196</v>
       </c>
-      <c r="E6" s="70" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="F6" s="70" t="inlineStr">
+      <c r="F6" s="72" t="inlineStr">
         <is>
           <t>initial seed record</t>
         </is>
       </c>
-      <c r="G6" s="70" t="inlineStr"/>
-      <c r="H6" s="70" t="inlineStr"/>
-      <c r="I6" s="70" t="inlineStr"/>
-      <c r="J6" s="70" t="inlineStr"/>
-      <c r="K6" s="70" t="inlineStr"/>
-      <c r="L6" s="70" t="inlineStr"/>
-      <c r="M6" s="70" t="inlineStr"/>
-      <c r="N6" s="70" t="inlineStr"/>
-      <c r="O6" s="70" t="inlineStr"/>
-      <c r="P6" s="70" t="inlineStr"/>
-      <c r="Q6" s="70" t="inlineStr"/>
-      <c r="R6" s="70" t="inlineStr"/>
-      <c r="S6" s="70" t="inlineStr"/>
-      <c r="T6" s="70" t="inlineStr"/>
-      <c r="U6" s="70" t="inlineStr"/>
-      <c r="V6" s="70" t="inlineStr"/>
-      <c r="W6" s="70" t="inlineStr"/>
-      <c r="X6" s="70" t="inlineStr"/>
-      <c r="Y6" s="70" t="inlineStr"/>
-      <c r="Z6" s="70" t="inlineStr"/>
-      <c r="AA6" s="70" t="inlineStr"/>
-      <c r="AB6" s="70" t="inlineStr"/>
-      <c r="AC6" s="70" t="inlineStr"/>
-      <c r="AD6" s="70" t="inlineStr"/>
-      <c r="AE6" s="70" t="inlineStr"/>
-      <c r="AF6" s="70" t="inlineStr"/>
-      <c r="AG6" s="70" t="inlineStr"/>
-      <c r="AH6" s="70" t="inlineStr"/>
-      <c r="AI6" s="70" t="inlineStr"/>
-      <c r="AJ6" s="70" t="inlineStr"/>
-      <c r="AK6" s="70" t="inlineStr"/>
-      <c r="AL6" s="70" t="inlineStr"/>
-      <c r="AM6" s="70" t="inlineStr"/>
-      <c r="AN6" s="70" t="inlineStr"/>
-      <c r="AO6" s="70" t="inlineStr"/>
-      <c r="AP6" s="70" t="inlineStr"/>
-      <c r="AQ6" s="70" t="inlineStr"/>
-      <c r="AR6" s="70" t="inlineStr"/>
-      <c r="AS6" s="70" t="inlineStr"/>
-      <c r="AT6" s="70" t="inlineStr"/>
-      <c r="AU6" s="70" t="inlineStr"/>
-      <c r="AV6" s="70" t="inlineStr"/>
-      <c r="AW6" s="70" t="inlineStr"/>
-      <c r="AX6" s="70" t="inlineStr"/>
-      <c r="AY6" s="70" t="inlineStr"/>
-      <c r="AZ6" s="70" t="inlineStr"/>
-      <c r="BA6" s="70" t="inlineStr"/>
-      <c r="BB6" s="70" t="inlineStr"/>
-      <c r="BC6" s="70" t="inlineStr"/>
-      <c r="BD6" s="70" t="inlineStr"/>
-      <c r="BE6" s="70" t="inlineStr"/>
-      <c r="BF6" s="70" t="inlineStr"/>
-      <c r="BG6" s="70" t="inlineStr"/>
-      <c r="BH6" s="70" t="inlineStr"/>
-      <c r="BI6" s="70" t="inlineStr"/>
-      <c r="BJ6" s="70" t="inlineStr"/>
-      <c r="BK6" s="70" t="inlineStr"/>
-      <c r="BL6" s="70" t="inlineStr"/>
-      <c r="BM6" s="70" t="inlineStr"/>
-      <c r="BN6" s="70" t="inlineStr"/>
-      <c r="BO6" s="70" t="inlineStr"/>
-      <c r="BP6" s="70" t="inlineStr"/>
-      <c r="BQ6" s="70" t="inlineStr"/>
-      <c r="BR6" s="70" t="inlineStr"/>
-      <c r="BS6" s="70" t="inlineStr"/>
-      <c r="BT6" s="70" t="inlineStr"/>
-      <c r="BU6" s="70" t="inlineStr"/>
-      <c r="BV6" s="70" t="inlineStr"/>
+      <c r="G6" s="72" t="inlineStr"/>
+      <c r="H6" s="72" t="inlineStr"/>
+      <c r="I6" s="72" t="inlineStr"/>
+      <c r="J6" s="72" t="inlineStr"/>
+      <c r="K6" s="72" t="inlineStr"/>
+      <c r="L6" s="72" t="inlineStr"/>
+      <c r="M6" s="72" t="inlineStr"/>
+      <c r="N6" s="72" t="inlineStr"/>
+      <c r="O6" s="72" t="inlineStr"/>
+      <c r="P6" s="72" t="inlineStr"/>
+      <c r="Q6" s="72" t="inlineStr"/>
+      <c r="R6" s="72" t="inlineStr"/>
+      <c r="S6" s="72" t="inlineStr"/>
+      <c r="T6" s="72" t="inlineStr"/>
+      <c r="U6" s="72" t="inlineStr"/>
+      <c r="V6" s="72" t="inlineStr"/>
+      <c r="W6" s="72" t="inlineStr"/>
+      <c r="X6" s="72" t="inlineStr"/>
+      <c r="Y6" s="72" t="inlineStr"/>
+      <c r="Z6" s="72" t="inlineStr"/>
+      <c r="AA6" s="72" t="inlineStr"/>
+      <c r="AB6" s="72" t="inlineStr"/>
+      <c r="AC6" s="72" t="inlineStr"/>
+      <c r="AD6" s="72" t="inlineStr"/>
+      <c r="AE6" s="72" t="inlineStr"/>
+      <c r="AF6" s="72" t="inlineStr"/>
+      <c r="AG6" s="72" t="inlineStr"/>
+      <c r="AH6" s="72" t="inlineStr"/>
+      <c r="AI6" s="72" t="inlineStr"/>
+      <c r="AJ6" s="72" t="inlineStr"/>
+      <c r="AK6" s="72" t="inlineStr"/>
+      <c r="AL6" s="72" t="inlineStr"/>
+      <c r="AM6" s="72" t="inlineStr"/>
+      <c r="AN6" s="72" t="inlineStr"/>
+      <c r="AO6" s="72" t="inlineStr"/>
+      <c r="AP6" s="72" t="inlineStr"/>
+      <c r="AQ6" s="72" t="inlineStr"/>
+      <c r="AR6" s="72" t="inlineStr"/>
+      <c r="AS6" s="72" t="inlineStr"/>
+      <c r="AT6" s="72" t="inlineStr"/>
+      <c r="AU6" s="72" t="inlineStr"/>
+      <c r="AV6" s="72" t="inlineStr"/>
+      <c r="AW6" s="72" t="inlineStr"/>
+      <c r="AX6" s="72" t="inlineStr"/>
+      <c r="AY6" s="72" t="inlineStr"/>
+      <c r="AZ6" s="72" t="inlineStr"/>
+      <c r="BA6" s="72" t="inlineStr"/>
+      <c r="BB6" s="72" t="inlineStr"/>
+      <c r="BC6" s="72" t="inlineStr"/>
+      <c r="BD6" s="72" t="inlineStr"/>
+      <c r="BE6" s="72" t="inlineStr"/>
+      <c r="BF6" s="72" t="inlineStr"/>
+      <c r="BG6" s="72" t="inlineStr"/>
+      <c r="BH6" s="72" t="inlineStr"/>
+      <c r="BI6" s="72" t="inlineStr"/>
+      <c r="BJ6" s="72" t="inlineStr"/>
+      <c r="BK6" s="72" t="inlineStr"/>
+      <c r="BL6" s="72" t="inlineStr"/>
+      <c r="BM6" s="72" t="inlineStr"/>
+      <c r="BN6" s="72" t="inlineStr"/>
+      <c r="BO6" s="72" t="inlineStr"/>
+      <c r="BP6" s="72" t="inlineStr"/>
+      <c r="BQ6" s="72" t="inlineStr"/>
+      <c r="BR6" s="72" t="inlineStr"/>
+      <c r="BS6" s="72" t="inlineStr"/>
+      <c r="BT6" s="72" t="inlineStr"/>
+      <c r="BU6" s="72" t="inlineStr"/>
+      <c r="BV6" s="72" t="inlineStr"/>
+      <c r="BW6" s="72" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="70" t="n">
+      <c r="A7" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Live Local A</t>
         </is>
       </c>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="C7" s="72" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="73" t="n">
         <v>46196</v>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="F7" s="70" t="inlineStr">
+      <c r="F7" s="72" t="inlineStr">
         <is>
           <t>initial seed record</t>
         </is>
       </c>
-      <c r="G7" s="70" t="inlineStr"/>
-      <c r="H7" s="70" t="inlineStr"/>
-      <c r="I7" s="70" t="inlineStr"/>
-      <c r="J7" s="70" t="inlineStr"/>
-      <c r="K7" s="70" t="inlineStr"/>
-      <c r="L7" s="70" t="inlineStr"/>
-      <c r="M7" s="70" t="inlineStr"/>
-      <c r="N7" s="70" t="inlineStr"/>
-      <c r="O7" s="70" t="inlineStr"/>
-      <c r="P7" s="70" t="inlineStr"/>
-      <c r="Q7" s="70" t="inlineStr"/>
-      <c r="R7" s="70" t="inlineStr"/>
-      <c r="S7" s="70" t="inlineStr"/>
-      <c r="T7" s="70" t="inlineStr"/>
-      <c r="U7" s="70" t="inlineStr"/>
-      <c r="V7" s="70" t="inlineStr"/>
-      <c r="W7" s="70" t="inlineStr"/>
-      <c r="X7" s="70" t="inlineStr"/>
-      <c r="Y7" s="70" t="inlineStr"/>
-      <c r="Z7" s="70" t="inlineStr"/>
-      <c r="AA7" s="70" t="inlineStr"/>
-      <c r="AB7" s="70" t="inlineStr"/>
-      <c r="AC7" s="70" t="inlineStr"/>
-      <c r="AD7" s="70" t="inlineStr"/>
-      <c r="AE7" s="70" t="inlineStr"/>
-      <c r="AF7" s="70" t="inlineStr"/>
-      <c r="AG7" s="70" t="inlineStr"/>
-      <c r="AH7" s="70" t="inlineStr"/>
-      <c r="AI7" s="70" t="inlineStr"/>
-      <c r="AJ7" s="70" t="inlineStr"/>
-      <c r="AK7" s="70" t="inlineStr"/>
-      <c r="AL7" s="70" t="inlineStr"/>
-      <c r="AM7" s="70" t="inlineStr"/>
-      <c r="AN7" s="70" t="inlineStr"/>
-      <c r="AO7" s="70" t="inlineStr"/>
-      <c r="AP7" s="70" t="inlineStr"/>
-      <c r="AQ7" s="70" t="inlineStr"/>
-      <c r="AR7" s="70" t="inlineStr"/>
-      <c r="AS7" s="70" t="inlineStr"/>
-      <c r="AT7" s="70" t="inlineStr"/>
-      <c r="AU7" s="70" t="inlineStr"/>
-      <c r="AV7" s="70" t="inlineStr"/>
-      <c r="AW7" s="70" t="inlineStr"/>
-      <c r="AX7" s="70" t="inlineStr"/>
-      <c r="AY7" s="70" t="inlineStr"/>
-      <c r="AZ7" s="70" t="inlineStr"/>
-      <c r="BA7" s="70" t="inlineStr"/>
-      <c r="BB7" s="70" t="inlineStr"/>
-      <c r="BC7" s="70" t="inlineStr"/>
-      <c r="BD7" s="70" t="inlineStr"/>
-      <c r="BE7" s="70" t="inlineStr"/>
-      <c r="BF7" s="70" t="inlineStr"/>
-      <c r="BG7" s="70" t="inlineStr"/>
-      <c r="BH7" s="70" t="inlineStr"/>
-      <c r="BI7" s="70" t="inlineStr"/>
-      <c r="BJ7" s="70" t="inlineStr"/>
-      <c r="BK7" s="70" t="inlineStr"/>
-      <c r="BL7" s="70" t="inlineStr"/>
-      <c r="BM7" s="70" t="inlineStr"/>
-      <c r="BN7" s="70" t="inlineStr"/>
-      <c r="BO7" s="70" t="inlineStr"/>
-      <c r="BP7" s="70" t="inlineStr"/>
-      <c r="BQ7" s="70" t="inlineStr"/>
-      <c r="BR7" s="70" t="inlineStr"/>
-      <c r="BS7" s="70" t="inlineStr"/>
-      <c r="BT7" s="70" t="inlineStr"/>
-      <c r="BU7" s="70" t="inlineStr"/>
-      <c r="BV7" s="70" t="inlineStr"/>
+      <c r="G7" s="72" t="inlineStr"/>
+      <c r="H7" s="72" t="inlineStr"/>
+      <c r="I7" s="72" t="inlineStr"/>
+      <c r="J7" s="72" t="inlineStr"/>
+      <c r="K7" s="72" t="inlineStr"/>
+      <c r="L7" s="72" t="inlineStr"/>
+      <c r="M7" s="72" t="inlineStr"/>
+      <c r="N7" s="72" t="inlineStr"/>
+      <c r="O7" s="72" t="inlineStr"/>
+      <c r="P7" s="72" t="inlineStr"/>
+      <c r="Q7" s="72" t="inlineStr"/>
+      <c r="R7" s="72" t="inlineStr"/>
+      <c r="S7" s="72" t="inlineStr"/>
+      <c r="T7" s="72" t="inlineStr"/>
+      <c r="U7" s="72" t="inlineStr"/>
+      <c r="V7" s="72" t="inlineStr"/>
+      <c r="W7" s="72" t="inlineStr"/>
+      <c r="X7" s="72" t="inlineStr"/>
+      <c r="Y7" s="72" t="inlineStr"/>
+      <c r="Z7" s="72" t="inlineStr"/>
+      <c r="AA7" s="72" t="inlineStr"/>
+      <c r="AB7" s="72" t="inlineStr"/>
+      <c r="AC7" s="72" t="inlineStr"/>
+      <c r="AD7" s="72" t="inlineStr"/>
+      <c r="AE7" s="72" t="inlineStr"/>
+      <c r="AF7" s="72" t="inlineStr"/>
+      <c r="AG7" s="72" t="inlineStr"/>
+      <c r="AH7" s="72" t="inlineStr"/>
+      <c r="AI7" s="72" t="inlineStr"/>
+      <c r="AJ7" s="72" t="inlineStr"/>
+      <c r="AK7" s="72" t="inlineStr"/>
+      <c r="AL7" s="72" t="inlineStr"/>
+      <c r="AM7" s="72" t="inlineStr"/>
+      <c r="AN7" s="72" t="inlineStr"/>
+      <c r="AO7" s="72" t="inlineStr"/>
+      <c r="AP7" s="72" t="inlineStr"/>
+      <c r="AQ7" s="72" t="inlineStr"/>
+      <c r="AR7" s="72" t="inlineStr"/>
+      <c r="AS7" s="72" t="inlineStr"/>
+      <c r="AT7" s="72" t="inlineStr"/>
+      <c r="AU7" s="72" t="inlineStr"/>
+      <c r="AV7" s="72" t="inlineStr"/>
+      <c r="AW7" s="72" t="inlineStr"/>
+      <c r="AX7" s="72" t="inlineStr"/>
+      <c r="AY7" s="72" t="inlineStr"/>
+      <c r="AZ7" s="72" t="inlineStr"/>
+      <c r="BA7" s="72" t="inlineStr"/>
+      <c r="BB7" s="72" t="inlineStr"/>
+      <c r="BC7" s="72" t="inlineStr"/>
+      <c r="BD7" s="72" t="inlineStr"/>
+      <c r="BE7" s="72" t="inlineStr"/>
+      <c r="BF7" s="72" t="inlineStr"/>
+      <c r="BG7" s="72" t="inlineStr"/>
+      <c r="BH7" s="72" t="inlineStr"/>
+      <c r="BI7" s="72" t="inlineStr"/>
+      <c r="BJ7" s="72" t="inlineStr"/>
+      <c r="BK7" s="72" t="inlineStr"/>
+      <c r="BL7" s="72" t="inlineStr"/>
+      <c r="BM7" s="72" t="inlineStr"/>
+      <c r="BN7" s="72" t="inlineStr"/>
+      <c r="BO7" s="72" t="inlineStr"/>
+      <c r="BP7" s="72" t="inlineStr"/>
+      <c r="BQ7" s="72" t="inlineStr"/>
+      <c r="BR7" s="72" t="inlineStr"/>
+      <c r="BS7" s="72" t="inlineStr"/>
+      <c r="BT7" s="72" t="inlineStr"/>
+      <c r="BU7" s="72" t="inlineStr"/>
+      <c r="BV7" s="72" t="inlineStr"/>
+      <c r="BW7" s="72" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -4287,915 +4426,915 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>PORTFOLIO DASHBOARD  -  all projects (latest published record), read-only</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="74" t="inlineStr">
         <is>
           <t>Phase No.</t>
         </is>
       </c>
-      <c r="C3" s="72" t="inlineStr">
+      <c r="C3" s="74" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="74" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="74" t="inlineStr">
         <is>
           <t>EGR</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="74" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G3" s="72" t="inlineStr">
+      <c r="G3" s="74" t="inlineStr">
         <is>
           <t>OpEx Ratio</t>
         </is>
       </c>
-      <c r="H3" s="72" t="inlineStr">
+      <c r="H3" s="74" t="inlineStr">
         <is>
           <t>Total Dev Cost</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="74" t="inlineStr">
         <is>
           <t>Cost/Unit</t>
         </is>
       </c>
-      <c r="J3" s="72" t="inlineStr">
+      <c r="J3" s="74" t="inlineStr">
         <is>
           <t>Yield on Cost</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="73">
+      <c r="A4" s="75">
         <f>IF(Lists!$A$2="","",Lists!$A$2)</f>
         <v/>
       </c>
-      <c r="B4" s="74">
+      <c r="B4" s="76">
         <f>IFERROR(IF(Lists!$A$2="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C4" s="74">
-        <f>IFERROR(IF(Lists!$A$2="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D4" s="74">
+      <c r="C4" s="76">
+        <f>IFERROR(IF(Lists!$A$2="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="76">
         <f>IFERROR(IF(Lists!$A$2="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$2),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E4" s="75">
+      <c r="E4" s="77">
         <f>IF(Lists!$A$2="","","-")</f>
         <v/>
       </c>
-      <c r="F4" s="75">
+      <c r="F4" s="77">
         <f>IF(Lists!$A$2="","","-")</f>
         <v/>
       </c>
-      <c r="G4" s="75">
+      <c r="G4" s="77">
         <f>IF(Lists!$A$2="","","-")</f>
         <v/>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="77">
         <f>IF(Lists!$A$2="","","-")</f>
         <v/>
       </c>
-      <c r="I4" s="75">
+      <c r="I4" s="77">
         <f>IF(Lists!$A$2="","","-")</f>
         <v/>
       </c>
-      <c r="J4" s="75">
+      <c r="J4" s="77">
         <f>IF(Lists!$A$2="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="73">
+      <c r="A5" s="75">
         <f>IF(Lists!$A$3="","",Lists!$A$3)</f>
         <v/>
       </c>
-      <c r="B5" s="74">
+      <c r="B5" s="76">
         <f>IFERROR(IF(Lists!$A$3="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C5" s="74">
-        <f>IFERROR(IF(Lists!$A$3="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="74">
+      <c r="C5" s="76">
+        <f>IFERROR(IF(Lists!$A$3="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="76">
         <f>IFERROR(IF(Lists!$A$3="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$3),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="77">
         <f>IF(Lists!$A$3="","","-")</f>
         <v/>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="77">
         <f>IF(Lists!$A$3="","","-")</f>
         <v/>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="77">
         <f>IF(Lists!$A$3="","","-")</f>
         <v/>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="77">
         <f>IF(Lists!$A$3="","","-")</f>
         <v/>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="77">
         <f>IF(Lists!$A$3="","","-")</f>
         <v/>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="77">
         <f>IF(Lists!$A$3="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73">
+      <c r="A6" s="75">
         <f>IF(Lists!$A$4="","",Lists!$A$4)</f>
         <v/>
       </c>
-      <c r="B6" s="74">
+      <c r="B6" s="76">
         <f>IFERROR(IF(Lists!$A$4="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C6" s="74">
-        <f>IFERROR(IF(Lists!$A$4="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="74">
+      <c r="C6" s="76">
+        <f>IFERROR(IF(Lists!$A$4="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="76">
         <f>IFERROR(IF(Lists!$A$4="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$4),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="77">
         <f>IF(Lists!$A$4="","","-")</f>
         <v/>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="77">
         <f>IF(Lists!$A$4="","","-")</f>
         <v/>
       </c>
-      <c r="G6" s="75">
+      <c r="G6" s="77">
         <f>IF(Lists!$A$4="","","-")</f>
         <v/>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="77">
         <f>IF(Lists!$A$4="","","-")</f>
         <v/>
       </c>
-      <c r="I6" s="75">
+      <c r="I6" s="77">
         <f>IF(Lists!$A$4="","","-")</f>
         <v/>
       </c>
-      <c r="J6" s="75">
+      <c r="J6" s="77">
         <f>IF(Lists!$A$4="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="73">
+      <c r="A7" s="75">
         <f>IF(Lists!$A$5="","",Lists!$A$5)</f>
         <v/>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="76">
         <f>IFERROR(IF(Lists!$A$5="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C7" s="74">
-        <f>IFERROR(IF(Lists!$A$5="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D7" s="74">
+      <c r="C7" s="76">
+        <f>IFERROR(IF(Lists!$A$5="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="76">
         <f>IFERROR(IF(Lists!$A$5="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$5),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="77">
         <f>IF(Lists!$A$5="","","-")</f>
         <v/>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="77">
         <f>IF(Lists!$A$5="","","-")</f>
         <v/>
       </c>
-      <c r="G7" s="75">
+      <c r="G7" s="77">
         <f>IF(Lists!$A$5="","","-")</f>
         <v/>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="77">
         <f>IF(Lists!$A$5="","","-")</f>
         <v/>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="77">
         <f>IF(Lists!$A$5="","","-")</f>
         <v/>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="77">
         <f>IF(Lists!$A$5="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="73">
+      <c r="A8" s="75">
         <f>IF(Lists!$A$6="","",Lists!$A$6)</f>
         <v/>
       </c>
-      <c r="B8" s="74">
+      <c r="B8" s="76">
         <f>IFERROR(IF(Lists!$A$6="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C8" s="74">
-        <f>IFERROR(IF(Lists!$A$6="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="74">
+      <c r="C8" s="76">
+        <f>IFERROR(IF(Lists!$A$6="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="76">
         <f>IFERROR(IF(Lists!$A$6="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$6),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="77">
         <f>IF(Lists!$A$6="","","-")</f>
         <v/>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="77">
         <f>IF(Lists!$A$6="","","-")</f>
         <v/>
       </c>
-      <c r="G8" s="75">
+      <c r="G8" s="77">
         <f>IF(Lists!$A$6="","","-")</f>
         <v/>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="77">
         <f>IF(Lists!$A$6="","","-")</f>
         <v/>
       </c>
-      <c r="I8" s="75">
+      <c r="I8" s="77">
         <f>IF(Lists!$A$6="","","-")</f>
         <v/>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="77">
         <f>IF(Lists!$A$6="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73">
+      <c r="A9" s="75">
         <f>IF(Lists!$A$7="","",Lists!$A$7)</f>
         <v/>
       </c>
-      <c r="B9" s="74">
+      <c r="B9" s="76">
         <f>IFERROR(IF(Lists!$A$7="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C9" s="74">
-        <f>IFERROR(IF(Lists!$A$7="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="74">
+      <c r="C9" s="76">
+        <f>IFERROR(IF(Lists!$A$7="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="76">
         <f>IFERROR(IF(Lists!$A$7="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$7),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="77">
         <f>IF(Lists!$A$7="","","-")</f>
         <v/>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="77">
         <f>IF(Lists!$A$7="","","-")</f>
         <v/>
       </c>
-      <c r="G9" s="75">
+      <c r="G9" s="77">
         <f>IF(Lists!$A$7="","","-")</f>
         <v/>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="77">
         <f>IF(Lists!$A$7="","","-")</f>
         <v/>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="77">
         <f>IF(Lists!$A$7="","","-")</f>
         <v/>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="77">
         <f>IF(Lists!$A$7="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73">
+      <c r="A10" s="75">
         <f>IF(Lists!$A$8="","",Lists!$A$8)</f>
         <v/>
       </c>
-      <c r="B10" s="74">
+      <c r="B10" s="76">
         <f>IFERROR(IF(Lists!$A$8="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C10" s="74">
-        <f>IFERROR(IF(Lists!$A$8="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="74">
+      <c r="C10" s="76">
+        <f>IFERROR(IF(Lists!$A$8="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="76">
         <f>IFERROR(IF(Lists!$A$8="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$8),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="77">
         <f>IF(Lists!$A$8="","","-")</f>
         <v/>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="77">
         <f>IF(Lists!$A$8="","","-")</f>
         <v/>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="77">
         <f>IF(Lists!$A$8="","","-")</f>
         <v/>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="77">
         <f>IF(Lists!$A$8="","","-")</f>
         <v/>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="77">
         <f>IF(Lists!$A$8="","","-")</f>
         <v/>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="77">
         <f>IF(Lists!$A$8="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73">
+      <c r="A11" s="75">
         <f>IF(Lists!$A$9="","",Lists!$A$9)</f>
         <v/>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="76">
         <f>IFERROR(IF(Lists!$A$9="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C11" s="74">
-        <f>IFERROR(IF(Lists!$A$9="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="74">
+      <c r="C11" s="76">
+        <f>IFERROR(IF(Lists!$A$9="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="76">
         <f>IFERROR(IF(Lists!$A$9="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$9),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="77">
         <f>IF(Lists!$A$9="","","-")</f>
         <v/>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="77">
         <f>IF(Lists!$A$9="","","-")</f>
         <v/>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="77">
         <f>IF(Lists!$A$9="","","-")</f>
         <v/>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="77">
         <f>IF(Lists!$A$9="","","-")</f>
         <v/>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="77">
         <f>IF(Lists!$A$9="","","-")</f>
         <v/>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="77">
         <f>IF(Lists!$A$9="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73">
+      <c r="A12" s="75">
         <f>IF(Lists!$A$10="","",Lists!$A$10)</f>
         <v/>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="76">
         <f>IFERROR(IF(Lists!$A$10="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C12" s="74">
-        <f>IFERROR(IF(Lists!$A$10="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="74">
+      <c r="C12" s="76">
+        <f>IFERROR(IF(Lists!$A$10="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="76">
         <f>IFERROR(IF(Lists!$A$10="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$10),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="77">
         <f>IF(Lists!$A$10="","","-")</f>
         <v/>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="77">
         <f>IF(Lists!$A$10="","","-")</f>
         <v/>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="77">
         <f>IF(Lists!$A$10="","","-")</f>
         <v/>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="77">
         <f>IF(Lists!$A$10="","","-")</f>
         <v/>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="77">
         <f>IF(Lists!$A$10="","","-")</f>
         <v/>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="77">
         <f>IF(Lists!$A$10="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="73">
+      <c r="A13" s="75">
         <f>IF(Lists!$A$11="","",Lists!$A$11)</f>
         <v/>
       </c>
-      <c r="B13" s="74">
+      <c r="B13" s="76">
         <f>IFERROR(IF(Lists!$A$11="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C13" s="74">
-        <f>IFERROR(IF(Lists!$A$11="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="74">
+      <c r="C13" s="76">
+        <f>IFERROR(IF(Lists!$A$11="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="76">
         <f>IFERROR(IF(Lists!$A$11="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$11),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="77">
         <f>IF(Lists!$A$11="","","-")</f>
         <v/>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="77">
         <f>IF(Lists!$A$11="","","-")</f>
         <v/>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="77">
         <f>IF(Lists!$A$11="","","-")</f>
         <v/>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="77">
         <f>IF(Lists!$A$11="","","-")</f>
         <v/>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="77">
         <f>IF(Lists!$A$11="","","-")</f>
         <v/>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="77">
         <f>IF(Lists!$A$11="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="73">
+      <c r="A14" s="75">
         <f>IF(Lists!$A$12="","",Lists!$A$12)</f>
         <v/>
       </c>
-      <c r="B14" s="74">
+      <c r="B14" s="76">
         <f>IFERROR(IF(Lists!$A$12="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C14" s="74">
-        <f>IFERROR(IF(Lists!$A$12="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="74">
+      <c r="C14" s="76">
+        <f>IFERROR(IF(Lists!$A$12="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="76">
         <f>IFERROR(IF(Lists!$A$12="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$12),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="77">
         <f>IF(Lists!$A$12="","","-")</f>
         <v/>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="77">
         <f>IF(Lists!$A$12="","","-")</f>
         <v/>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="77">
         <f>IF(Lists!$A$12="","","-")</f>
         <v/>
       </c>
-      <c r="H14" s="75">
+      <c r="H14" s="77">
         <f>IF(Lists!$A$12="","","-")</f>
         <v/>
       </c>
-      <c r="I14" s="75">
+      <c r="I14" s="77">
         <f>IF(Lists!$A$12="","","-")</f>
         <v/>
       </c>
-      <c r="J14" s="75">
+      <c r="J14" s="77">
         <f>IF(Lists!$A$12="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="73">
+      <c r="A15" s="75">
         <f>IF(Lists!$A$13="","",Lists!$A$13)</f>
         <v/>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="76">
         <f>IFERROR(IF(Lists!$A$13="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C15" s="74">
-        <f>IFERROR(IF(Lists!$A$13="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="74">
+      <c r="C15" s="76">
+        <f>IFERROR(IF(Lists!$A$13="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="76">
         <f>IFERROR(IF(Lists!$A$13="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$13),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="77">
         <f>IF(Lists!$A$13="","","-")</f>
         <v/>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="77">
         <f>IF(Lists!$A$13="","","-")</f>
         <v/>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="77">
         <f>IF(Lists!$A$13="","","-")</f>
         <v/>
       </c>
-      <c r="H15" s="75">
+      <c r="H15" s="77">
         <f>IF(Lists!$A$13="","","-")</f>
         <v/>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="77">
         <f>IF(Lists!$A$13="","","-")</f>
         <v/>
       </c>
-      <c r="J15" s="75">
+      <c r="J15" s="77">
         <f>IF(Lists!$A$13="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="73">
+      <c r="A16" s="75">
         <f>IF(Lists!$A$14="","",Lists!$A$14)</f>
         <v/>
       </c>
-      <c r="B16" s="74">
+      <c r="B16" s="76">
         <f>IFERROR(IF(Lists!$A$14="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C16" s="74">
-        <f>IFERROR(IF(Lists!$A$14="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="74">
+      <c r="C16" s="76">
+        <f>IFERROR(IF(Lists!$A$14="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="76">
         <f>IFERROR(IF(Lists!$A$14="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$14),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E16" s="75">
+      <c r="E16" s="77">
         <f>IF(Lists!$A$14="","","-")</f>
         <v/>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="77">
         <f>IF(Lists!$A$14="","","-")</f>
         <v/>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="77">
         <f>IF(Lists!$A$14="","","-")</f>
         <v/>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="77">
         <f>IF(Lists!$A$14="","","-")</f>
         <v/>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="77">
         <f>IF(Lists!$A$14="","","-")</f>
         <v/>
       </c>
-      <c r="J16" s="75">
+      <c r="J16" s="77">
         <f>IF(Lists!$A$14="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="73">
+      <c r="A17" s="75">
         <f>IF(Lists!$A$15="","",Lists!$A$15)</f>
         <v/>
       </c>
-      <c r="B17" s="74">
+      <c r="B17" s="76">
         <f>IFERROR(IF(Lists!$A$15="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C17" s="74">
-        <f>IFERROR(IF(Lists!$A$15="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="74">
+      <c r="C17" s="76">
+        <f>IFERROR(IF(Lists!$A$15="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="76">
         <f>IFERROR(IF(Lists!$A$15="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$15),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E17" s="75">
+      <c r="E17" s="77">
         <f>IF(Lists!$A$15="","","-")</f>
         <v/>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="77">
         <f>IF(Lists!$A$15="","","-")</f>
         <v/>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="77">
         <f>IF(Lists!$A$15="","","-")</f>
         <v/>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="77">
         <f>IF(Lists!$A$15="","","-")</f>
         <v/>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="77">
         <f>IF(Lists!$A$15="","","-")</f>
         <v/>
       </c>
-      <c r="J17" s="75">
+      <c r="J17" s="77">
         <f>IF(Lists!$A$15="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="73">
+      <c r="A18" s="75">
         <f>IF(Lists!$A$16="","",Lists!$A$16)</f>
         <v/>
       </c>
-      <c r="B18" s="74">
+      <c r="B18" s="76">
         <f>IFERROR(IF(Lists!$A$16="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C18" s="74">
-        <f>IFERROR(IF(Lists!$A$16="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="74">
+      <c r="C18" s="76">
+        <f>IFERROR(IF(Lists!$A$16="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="76">
         <f>IFERROR(IF(Lists!$A$16="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$16),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="77">
         <f>IF(Lists!$A$16="","","-")</f>
         <v/>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="77">
         <f>IF(Lists!$A$16="","","-")</f>
         <v/>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="77">
         <f>IF(Lists!$A$16="","","-")</f>
         <v/>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="77">
         <f>IF(Lists!$A$16="","","-")</f>
         <v/>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="77">
         <f>IF(Lists!$A$16="","","-")</f>
         <v/>
       </c>
-      <c r="J18" s="75">
+      <c r="J18" s="77">
         <f>IF(Lists!$A$16="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="73">
+      <c r="A19" s="75">
         <f>IF(Lists!$A$17="","",Lists!$A$17)</f>
         <v/>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="76">
         <f>IFERROR(IF(Lists!$A$17="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C19" s="74">
-        <f>IFERROR(IF(Lists!$A$17="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="74">
+      <c r="C19" s="76">
+        <f>IFERROR(IF(Lists!$A$17="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="76">
         <f>IFERROR(IF(Lists!$A$17="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$17),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="77">
         <f>IF(Lists!$A$17="","","-")</f>
         <v/>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="77">
         <f>IF(Lists!$A$17="","","-")</f>
         <v/>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="77">
         <f>IF(Lists!$A$17="","","-")</f>
         <v/>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="77">
         <f>IF(Lists!$A$17="","","-")</f>
         <v/>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="77">
         <f>IF(Lists!$A$17="","","-")</f>
         <v/>
       </c>
-      <c r="J19" s="75">
+      <c r="J19" s="77">
         <f>IF(Lists!$A$17="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="73">
+      <c r="A20" s="75">
         <f>IF(Lists!$A$18="","",Lists!$A$18)</f>
         <v/>
       </c>
-      <c r="B20" s="74">
+      <c r="B20" s="76">
         <f>IFERROR(IF(Lists!$A$18="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C20" s="74">
-        <f>IFERROR(IF(Lists!$A$18="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="74">
+      <c r="C20" s="76">
+        <f>IFERROR(IF(Lists!$A$18="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="76">
         <f>IFERROR(IF(Lists!$A$18="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$18),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="77">
         <f>IF(Lists!$A$18="","","-")</f>
         <v/>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="77">
         <f>IF(Lists!$A$18="","","-")</f>
         <v/>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="77">
         <f>IF(Lists!$A$18="","","-")</f>
         <v/>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="77">
         <f>IF(Lists!$A$18="","","-")</f>
         <v/>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="77">
         <f>IF(Lists!$A$18="","","-")</f>
         <v/>
       </c>
-      <c r="J20" s="75">
+      <c r="J20" s="77">
         <f>IF(Lists!$A$18="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="73">
+      <c r="A21" s="75">
         <f>IF(Lists!$A$19="","",Lists!$A$19)</f>
         <v/>
       </c>
-      <c r="B21" s="74">
+      <c r="B21" s="76">
         <f>IFERROR(IF(Lists!$A$19="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C21" s="74">
-        <f>IFERROR(IF(Lists!$A$19="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="74">
+      <c r="C21" s="76">
+        <f>IFERROR(IF(Lists!$A$19="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="76">
         <f>IFERROR(IF(Lists!$A$19="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$19),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="77">
         <f>IF(Lists!$A$19="","","-")</f>
         <v/>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="77">
         <f>IF(Lists!$A$19="","","-")</f>
         <v/>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="77">
         <f>IF(Lists!$A$19="","","-")</f>
         <v/>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="77">
         <f>IF(Lists!$A$19="","","-")</f>
         <v/>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="77">
         <f>IF(Lists!$A$19="","","-")</f>
         <v/>
       </c>
-      <c r="J21" s="75">
+      <c r="J21" s="77">
         <f>IF(Lists!$A$19="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="73">
+      <c r="A22" s="75">
         <f>IF(Lists!$A$20="","",Lists!$A$20)</f>
         <v/>
       </c>
-      <c r="B22" s="74">
+      <c r="B22" s="76">
         <f>IFERROR(IF(Lists!$A$20="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C22" s="74">
-        <f>IFERROR(IF(Lists!$A$20="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="74">
+      <c r="C22" s="76">
+        <f>IFERROR(IF(Lists!$A$20="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="76">
         <f>IFERROR(IF(Lists!$A$20="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$20),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="77">
         <f>IF(Lists!$A$20="","","-")</f>
         <v/>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="77">
         <f>IF(Lists!$A$20="","","-")</f>
         <v/>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="77">
         <f>IF(Lists!$A$20="","","-")</f>
         <v/>
       </c>
-      <c r="H22" s="75">
+      <c r="H22" s="77">
         <f>IF(Lists!$A$20="","","-")</f>
         <v/>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="77">
         <f>IF(Lists!$A$20="","","-")</f>
         <v/>
       </c>
-      <c r="J22" s="75">
+      <c r="J22" s="77">
         <f>IF(Lists!$A$20="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="73">
+      <c r="A23" s="75">
         <f>IF(Lists!$A$21="","",Lists!$A$21)</f>
         <v/>
       </c>
-      <c r="B23" s="74">
+      <c r="B23" s="76">
         <f>IFERROR(IF(Lists!$A$21="","",INDEX(Database!$G:$G,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="C23" s="74">
-        <f>IFERROR(IF(Lists!$A$21="","",N(INDEX(Database!$Y:$Y,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))+N(INDEX(Database!$AC:$AC,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))+N(INDEX(Database!$AG:$AG,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))+N(INDEX(Database!$AK:$AK,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="74">
+      <c r="C23" s="76">
+        <f>IFERROR(IF(Lists!$A$21="","",N(INDEX(Database!$Z:$Z,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))+N(INDEX(Database!$AD:$AD,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))+N(INDEX(Database!$AH:$AH,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))+N(INDEX(Database!$AL:$AL,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="76">
         <f>IFERROR(IF(Lists!$A$21="","",INDEX(Database!$L:$L,MATCH(MAXIFS(Database!$A:$A,Database!$B:$B,Lists!$A$21),Database!$A:$A,0))),"")</f>
         <v/>
       </c>
-      <c r="E23" s="75">
+      <c r="E23" s="77">
         <f>IF(Lists!$A$21="","","-")</f>
         <v/>
       </c>
-      <c r="F23" s="75">
+      <c r="F23" s="77">
         <f>IF(Lists!$A$21="","","-")</f>
         <v/>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="77">
         <f>IF(Lists!$A$21="","","-")</f>
         <v/>
       </c>
-      <c r="H23" s="75">
+      <c r="H23" s="77">
         <f>IF(Lists!$A$21="","","-")</f>
         <v/>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="77">
         <f>IF(Lists!$A$21="","","-")</f>
         <v/>
       </c>
-      <c r="J23" s="75">
+      <c r="J23" s="77">
         <f>IF(Lists!$A$21="","","-")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>PORTFOLIO TOTAL</t>
         </is>
       </c>
-      <c r="C24" s="76">
+      <c r="C24" s="78">
         <f>SUM(C4:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="76">
+      <c r="D24" s="78">
         <f>SUM(D4:D23)</f>
         <v/>
       </c>
@@ -5223,7 +5362,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>PROJECT DASHBOARD  -  read-only single-project view (printable)</t>
         </is>
@@ -5242,97 +5381,97 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Renders the operating proforma for the selected project from the database latest record. (Full recompute wired with the calc engine next pass.)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Operating Proforma</t>
         </is>
       </c>
-      <c r="B7" s="78" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>$ Annual</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Gross Potential Rent</t>
         </is>
       </c>
-      <c r="B8" s="59">
+      <c r="B8" s="61">
         <f>"-"</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Effective Rental Revenue</t>
         </is>
       </c>
-      <c r="B9" s="59">
+      <c r="B9" s="61">
         <f>"-"</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B10" s="59">
+      <c r="B10" s="61">
         <f>"-"</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Effective Gross Revenue (EGR)</t>
         </is>
       </c>
-      <c r="B11" s="59">
+      <c r="B11" s="61">
         <f>"-"</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" s="61">
         <f>"-"</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B13" s="59">
+      <c r="B13" s="61">
         <f>"-"</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>OpEx Ratio</t>
         </is>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="63">
         <f>"-"</f>
         <v/>
       </c>
@@ -5358,14 +5497,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>MONTHLY CF  -  FUTURE calc engine placeholder (date spine only this pass)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Spine driven by the Console closing date for the selected project. Operating CFs / capital costs / unlevered CFs plug in below later.</t>
         </is>
@@ -5388,364 +5527,364 @@
           <t>Month index</t>
         </is>
       </c>
-      <c r="C6" s="80" t="n">
+      <c r="C6" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="80" t="n">
+      <c r="D6" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="80" t="n">
+      <c r="E6" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="80" t="n">
+      <c r="F6" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="80" t="n">
+      <c r="G6" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="80" t="n">
+      <c r="H6" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="80" t="n">
+      <c r="I6" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="80" t="n">
+      <c r="J6" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="80" t="n">
+      <c r="K6" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="80" t="n">
+      <c r="L6" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="80" t="n">
+      <c r="M6" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="80" t="n">
+      <c r="N6" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="80" t="n">
+      <c r="O6" s="81" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="80" t="n">
+      <c r="P6" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="80" t="n">
+      <c r="Q6" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="80" t="n">
+      <c r="R6" s="81" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="80" t="n">
+      <c r="S6" s="81" t="n">
         <v>17</v>
       </c>
-      <c r="T6" s="80" t="n">
+      <c r="T6" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="U6" s="80" t="n">
+      <c r="U6" s="81" t="n">
         <v>19</v>
       </c>
-      <c r="V6" s="80" t="n">
+      <c r="V6" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="W6" s="80" t="n">
+      <c r="W6" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="X6" s="80" t="n">
+      <c r="X6" s="81" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="80" t="n">
+      <c r="Y6" s="81" t="n">
         <v>23</v>
       </c>
-      <c r="Z6" s="80" t="n">
+      <c r="Z6" s="81" t="n">
         <v>24</v>
       </c>
-      <c r="AA6" s="80" t="n">
+      <c r="AA6" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="AB6" s="80" t="n">
+      <c r="AB6" s="81" t="n">
         <v>26</v>
       </c>
-      <c r="AC6" s="80" t="n">
+      <c r="AC6" s="81" t="n">
         <v>27</v>
       </c>
-      <c r="AD6" s="80" t="n">
+      <c r="AD6" s="81" t="n">
         <v>28</v>
       </c>
-      <c r="AE6" s="80" t="n">
+      <c r="AE6" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="AF6" s="80" t="n">
+      <c r="AF6" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="AG6" s="80" t="n">
+      <c r="AG6" s="81" t="n">
         <v>31</v>
       </c>
-      <c r="AH6" s="80" t="n">
+      <c r="AH6" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="AI6" s="80" t="n">
+      <c r="AI6" s="81" t="n">
         <v>33</v>
       </c>
-      <c r="AJ6" s="80" t="n">
+      <c r="AJ6" s="81" t="n">
         <v>34</v>
       </c>
-      <c r="AK6" s="80" t="n">
+      <c r="AK6" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="AL6" s="80" t="n">
+      <c r="AL6" s="81" t="n">
         <v>36</v>
       </c>
-      <c r="AM6" s="80" t="n">
+      <c r="AM6" s="81" t="n">
         <v>37</v>
       </c>
-      <c r="AN6" s="80" t="n">
+      <c r="AN6" s="81" t="n">
         <v>38</v>
       </c>
-      <c r="AO6" s="80" t="n">
+      <c r="AO6" s="81" t="n">
         <v>39</v>
       </c>
-      <c r="AP6" s="80" t="n">
+      <c r="AP6" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="AQ6" s="80" t="n">
+      <c r="AQ6" s="81" t="n">
         <v>41</v>
       </c>
-      <c r="AR6" s="80" t="n">
+      <c r="AR6" s="81" t="n">
         <v>42</v>
       </c>
-      <c r="AS6" s="80" t="n">
+      <c r="AS6" s="81" t="n">
         <v>43</v>
       </c>
-      <c r="AT6" s="80" t="n">
+      <c r="AT6" s="81" t="n">
         <v>44</v>
       </c>
-      <c r="AU6" s="80" t="n">
+      <c r="AU6" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="AV6" s="80" t="n">
+      <c r="AV6" s="81" t="n">
         <v>46</v>
       </c>
-      <c r="AW6" s="80" t="n">
+      <c r="AW6" s="81" t="n">
         <v>47</v>
       </c>
-      <c r="AX6" s="80" t="n">
+      <c r="AX6" s="81" t="n">
         <v>48</v>
       </c>
-      <c r="AY6" s="80" t="n">
+      <c r="AY6" s="81" t="n">
         <v>49</v>
       </c>
-      <c r="AZ6" s="80" t="n">
+      <c r="AZ6" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="BA6" s="80" t="n">
+      <c r="BA6" s="81" t="n">
         <v>51</v>
       </c>
-      <c r="BB6" s="80" t="n">
+      <c r="BB6" s="81" t="n">
         <v>52</v>
       </c>
-      <c r="BC6" s="80" t="n">
+      <c r="BC6" s="81" t="n">
         <v>53</v>
       </c>
-      <c r="BD6" s="80" t="n">
+      <c r="BD6" s="81" t="n">
         <v>54</v>
       </c>
-      <c r="BE6" s="80" t="n">
+      <c r="BE6" s="81" t="n">
         <v>55</v>
       </c>
-      <c r="BF6" s="80" t="n">
+      <c r="BF6" s="81" t="n">
         <v>56</v>
       </c>
-      <c r="BG6" s="80" t="n">
+      <c r="BG6" s="81" t="n">
         <v>57</v>
       </c>
-      <c r="BH6" s="80" t="n">
+      <c r="BH6" s="81" t="n">
         <v>58</v>
       </c>
-      <c r="BI6" s="80" t="n">
+      <c r="BI6" s="81" t="n">
         <v>59</v>
       </c>
-      <c r="BJ6" s="80" t="n">
+      <c r="BJ6" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="BK6" s="80" t="n">
+      <c r="BK6" s="81" t="n">
         <v>61</v>
       </c>
-      <c r="BL6" s="80" t="n">
+      <c r="BL6" s="81" t="n">
         <v>62</v>
       </c>
-      <c r="BM6" s="80" t="n">
+      <c r="BM6" s="81" t="n">
         <v>63</v>
       </c>
-      <c r="BN6" s="80" t="n">
+      <c r="BN6" s="81" t="n">
         <v>64</v>
       </c>
-      <c r="BO6" s="80" t="n">
+      <c r="BO6" s="81" t="n">
         <v>65</v>
       </c>
-      <c r="BP6" s="80" t="n">
+      <c r="BP6" s="81" t="n">
         <v>66</v>
       </c>
-      <c r="BQ6" s="80" t="n">
+      <c r="BQ6" s="81" t="n">
         <v>67</v>
       </c>
-      <c r="BR6" s="80" t="n">
+      <c r="BR6" s="81" t="n">
         <v>68</v>
       </c>
-      <c r="BS6" s="80" t="n">
+      <c r="BS6" s="81" t="n">
         <v>69</v>
       </c>
-      <c r="BT6" s="80" t="n">
+      <c r="BT6" s="81" t="n">
         <v>70</v>
       </c>
-      <c r="BU6" s="80" t="n">
+      <c r="BU6" s="81" t="n">
         <v>71</v>
       </c>
-      <c r="BV6" s="80" t="n">
+      <c r="BV6" s="81" t="n">
         <v>72</v>
       </c>
-      <c r="BW6" s="80" t="n">
+      <c r="BW6" s="81" t="n">
         <v>73</v>
       </c>
-      <c r="BX6" s="80" t="n">
+      <c r="BX6" s="81" t="n">
         <v>74</v>
       </c>
-      <c r="BY6" s="80" t="n">
+      <c r="BY6" s="81" t="n">
         <v>75</v>
       </c>
-      <c r="BZ6" s="80" t="n">
+      <c r="BZ6" s="81" t="n">
         <v>76</v>
       </c>
-      <c r="CA6" s="80" t="n">
+      <c r="CA6" s="81" t="n">
         <v>77</v>
       </c>
-      <c r="CB6" s="80" t="n">
+      <c r="CB6" s="81" t="n">
         <v>78</v>
       </c>
-      <c r="CC6" s="80" t="n">
+      <c r="CC6" s="81" t="n">
         <v>79</v>
       </c>
-      <c r="CD6" s="80" t="n">
+      <c r="CD6" s="81" t="n">
         <v>80</v>
       </c>
-      <c r="CE6" s="80" t="n">
+      <c r="CE6" s="81" t="n">
         <v>81</v>
       </c>
-      <c r="CF6" s="80" t="n">
+      <c r="CF6" s="81" t="n">
         <v>82</v>
       </c>
-      <c r="CG6" s="80" t="n">
+      <c r="CG6" s="81" t="n">
         <v>83</v>
       </c>
-      <c r="CH6" s="80" t="n">
+      <c r="CH6" s="81" t="n">
         <v>84</v>
       </c>
-      <c r="CI6" s="80" t="n">
+      <c r="CI6" s="81" t="n">
         <v>85</v>
       </c>
-      <c r="CJ6" s="80" t="n">
+      <c r="CJ6" s="81" t="n">
         <v>86</v>
       </c>
-      <c r="CK6" s="80" t="n">
+      <c r="CK6" s="81" t="n">
         <v>87</v>
       </c>
-      <c r="CL6" s="80" t="n">
+      <c r="CL6" s="81" t="n">
         <v>88</v>
       </c>
-      <c r="CM6" s="80" t="n">
+      <c r="CM6" s="81" t="n">
         <v>89</v>
       </c>
-      <c r="CN6" s="80" t="n">
+      <c r="CN6" s="81" t="n">
         <v>90</v>
       </c>
-      <c r="CO6" s="80" t="n">
+      <c r="CO6" s="81" t="n">
         <v>91</v>
       </c>
-      <c r="CP6" s="80" t="n">
+      <c r="CP6" s="81" t="n">
         <v>92</v>
       </c>
-      <c r="CQ6" s="80" t="n">
+      <c r="CQ6" s="81" t="n">
         <v>93</v>
       </c>
-      <c r="CR6" s="80" t="n">
+      <c r="CR6" s="81" t="n">
         <v>94</v>
       </c>
-      <c r="CS6" s="80" t="n">
+      <c r="CS6" s="81" t="n">
         <v>95</v>
       </c>
-      <c r="CT6" s="80" t="n">
+      <c r="CT6" s="81" t="n">
         <v>96</v>
       </c>
-      <c r="CU6" s="80" t="n">
+      <c r="CU6" s="81" t="n">
         <v>97</v>
       </c>
-      <c r="CV6" s="80" t="n">
+      <c r="CV6" s="81" t="n">
         <v>98</v>
       </c>
-      <c r="CW6" s="80" t="n">
+      <c r="CW6" s="81" t="n">
         <v>99</v>
       </c>
-      <c r="CX6" s="80" t="n">
+      <c r="CX6" s="81" t="n">
         <v>100</v>
       </c>
-      <c r="CY6" s="80" t="n">
+      <c r="CY6" s="81" t="n">
         <v>101</v>
       </c>
-      <c r="CZ6" s="80" t="n">
+      <c r="CZ6" s="81" t="n">
         <v>102</v>
       </c>
-      <c r="DA6" s="80" t="n">
+      <c r="DA6" s="81" t="n">
         <v>103</v>
       </c>
-      <c r="DB6" s="80" t="n">
+      <c r="DB6" s="81" t="n">
         <v>104</v>
       </c>
-      <c r="DC6" s="80" t="n">
+      <c r="DC6" s="81" t="n">
         <v>105</v>
       </c>
-      <c r="DD6" s="80" t="n">
+      <c r="DD6" s="81" t="n">
         <v>106</v>
       </c>
-      <c r="DE6" s="80" t="n">
+      <c r="DE6" s="81" t="n">
         <v>107</v>
       </c>
-      <c r="DF6" s="80" t="n">
+      <c r="DF6" s="81" t="n">
         <v>108</v>
       </c>
-      <c r="DG6" s="80" t="n">
+      <c r="DG6" s="81" t="n">
         <v>109</v>
       </c>
-      <c r="DH6" s="80" t="n">
+      <c r="DH6" s="81" t="n">
         <v>110</v>
       </c>
-      <c r="DI6" s="80" t="n">
+      <c r="DI6" s="81" t="n">
         <v>111</v>
       </c>
-      <c r="DJ6" s="80" t="n">
+      <c r="DJ6" s="81" t="n">
         <v>112</v>
       </c>
-      <c r="DK6" s="80" t="n">
+      <c r="DK6" s="81" t="n">
         <v>113</v>
       </c>
-      <c r="DL6" s="80" t="n">
+      <c r="DL6" s="81" t="n">
         <v>114</v>
       </c>
-      <c r="DM6" s="80" t="n">
+      <c r="DM6" s="81" t="n">
         <v>115</v>
       </c>
-      <c r="DN6" s="80" t="n">
+      <c r="DN6" s="81" t="n">
         <v>116</v>
       </c>
-      <c r="DO6" s="80" t="n">
+      <c r="DO6" s="81" t="n">
         <v>117</v>
       </c>
-      <c r="DP6" s="80" t="n">
+      <c r="DP6" s="81" t="n">
         <v>118</v>
       </c>
-      <c r="DQ6" s="80" t="n">
+      <c r="DQ6" s="81" t="n">
         <v>119</v>
       </c>
-      <c r="DR6" s="80" t="n">
+      <c r="DR6" s="81" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5755,483 +5894,483 @@
           <t>Month start</t>
         </is>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="82">
         <f>EDATE($B$4,0)</f>
         <v/>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="82">
         <f>EDATE($B$4,1)</f>
         <v/>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="82">
         <f>EDATE($B$4,2)</f>
         <v/>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="82">
         <f>EDATE($B$4,3)</f>
         <v/>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="82">
         <f>EDATE($B$4,4)</f>
         <v/>
       </c>
-      <c r="H7" s="81">
+      <c r="H7" s="82">
         <f>EDATE($B$4,5)</f>
         <v/>
       </c>
-      <c r="I7" s="81">
+      <c r="I7" s="82">
         <f>EDATE($B$4,6)</f>
         <v/>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="82">
         <f>EDATE($B$4,7)</f>
         <v/>
       </c>
-      <c r="K7" s="81">
+      <c r="K7" s="82">
         <f>EDATE($B$4,8)</f>
         <v/>
       </c>
-      <c r="L7" s="81">
+      <c r="L7" s="82">
         <f>EDATE($B$4,9)</f>
         <v/>
       </c>
-      <c r="M7" s="81">
+      <c r="M7" s="82">
         <f>EDATE($B$4,10)</f>
         <v/>
       </c>
-      <c r="N7" s="81">
+      <c r="N7" s="82">
         <f>EDATE($B$4,11)</f>
         <v/>
       </c>
-      <c r="O7" s="81">
+      <c r="O7" s="82">
         <f>EDATE($B$4,12)</f>
         <v/>
       </c>
-      <c r="P7" s="81">
+      <c r="P7" s="82">
         <f>EDATE($B$4,13)</f>
         <v/>
       </c>
-      <c r="Q7" s="81">
+      <c r="Q7" s="82">
         <f>EDATE($B$4,14)</f>
         <v/>
       </c>
-      <c r="R7" s="81">
+      <c r="R7" s="82">
         <f>EDATE($B$4,15)</f>
         <v/>
       </c>
-      <c r="S7" s="81">
+      <c r="S7" s="82">
         <f>EDATE($B$4,16)</f>
         <v/>
       </c>
-      <c r="T7" s="81">
+      <c r="T7" s="82">
         <f>EDATE($B$4,17)</f>
         <v/>
       </c>
-      <c r="U7" s="81">
+      <c r="U7" s="82">
         <f>EDATE($B$4,18)</f>
         <v/>
       </c>
-      <c r="V7" s="81">
+      <c r="V7" s="82">
         <f>EDATE($B$4,19)</f>
         <v/>
       </c>
-      <c r="W7" s="81">
+      <c r="W7" s="82">
         <f>EDATE($B$4,20)</f>
         <v/>
       </c>
-      <c r="X7" s="81">
+      <c r="X7" s="82">
         <f>EDATE($B$4,21)</f>
         <v/>
       </c>
-      <c r="Y7" s="81">
+      <c r="Y7" s="82">
         <f>EDATE($B$4,22)</f>
         <v/>
       </c>
-      <c r="Z7" s="81">
+      <c r="Z7" s="82">
         <f>EDATE($B$4,23)</f>
         <v/>
       </c>
-      <c r="AA7" s="81">
+      <c r="AA7" s="82">
         <f>EDATE($B$4,24)</f>
         <v/>
       </c>
-      <c r="AB7" s="81">
+      <c r="AB7" s="82">
         <f>EDATE($B$4,25)</f>
         <v/>
       </c>
-      <c r="AC7" s="81">
+      <c r="AC7" s="82">
         <f>EDATE($B$4,26)</f>
         <v/>
       </c>
-      <c r="AD7" s="81">
+      <c r="AD7" s="82">
         <f>EDATE($B$4,27)</f>
         <v/>
       </c>
-      <c r="AE7" s="81">
+      <c r="AE7" s="82">
         <f>EDATE($B$4,28)</f>
         <v/>
       </c>
-      <c r="AF7" s="81">
+      <c r="AF7" s="82">
         <f>EDATE($B$4,29)</f>
         <v/>
       </c>
-      <c r="AG7" s="81">
+      <c r="AG7" s="82">
         <f>EDATE($B$4,30)</f>
         <v/>
       </c>
-      <c r="AH7" s="81">
+      <c r="AH7" s="82">
         <f>EDATE($B$4,31)</f>
         <v/>
       </c>
-      <c r="AI7" s="81">
+      <c r="AI7" s="82">
         <f>EDATE($B$4,32)</f>
         <v/>
       </c>
-      <c r="AJ7" s="81">
+      <c r="AJ7" s="82">
         <f>EDATE($B$4,33)</f>
         <v/>
       </c>
-      <c r="AK7" s="81">
+      <c r="AK7" s="82">
         <f>EDATE($B$4,34)</f>
         <v/>
       </c>
-      <c r="AL7" s="81">
+      <c r="AL7" s="82">
         <f>EDATE($B$4,35)</f>
         <v/>
       </c>
-      <c r="AM7" s="81">
+      <c r="AM7" s="82">
         <f>EDATE($B$4,36)</f>
         <v/>
       </c>
-      <c r="AN7" s="81">
+      <c r="AN7" s="82">
         <f>EDATE($B$4,37)</f>
         <v/>
       </c>
-      <c r="AO7" s="81">
+      <c r="AO7" s="82">
         <f>EDATE($B$4,38)</f>
         <v/>
       </c>
-      <c r="AP7" s="81">
+      <c r="AP7" s="82">
         <f>EDATE($B$4,39)</f>
         <v/>
       </c>
-      <c r="AQ7" s="81">
+      <c r="AQ7" s="82">
         <f>EDATE($B$4,40)</f>
         <v/>
       </c>
-      <c r="AR7" s="81">
+      <c r="AR7" s="82">
         <f>EDATE($B$4,41)</f>
         <v/>
       </c>
-      <c r="AS7" s="81">
+      <c r="AS7" s="82">
         <f>EDATE($B$4,42)</f>
         <v/>
       </c>
-      <c r="AT7" s="81">
+      <c r="AT7" s="82">
         <f>EDATE($B$4,43)</f>
         <v/>
       </c>
-      <c r="AU7" s="81">
+      <c r="AU7" s="82">
         <f>EDATE($B$4,44)</f>
         <v/>
       </c>
-      <c r="AV7" s="81">
+      <c r="AV7" s="82">
         <f>EDATE($B$4,45)</f>
         <v/>
       </c>
-      <c r="AW7" s="81">
+      <c r="AW7" s="82">
         <f>EDATE($B$4,46)</f>
         <v/>
       </c>
-      <c r="AX7" s="81">
+      <c r="AX7" s="82">
         <f>EDATE($B$4,47)</f>
         <v/>
       </c>
-      <c r="AY7" s="81">
+      <c r="AY7" s="82">
         <f>EDATE($B$4,48)</f>
         <v/>
       </c>
-      <c r="AZ7" s="81">
+      <c r="AZ7" s="82">
         <f>EDATE($B$4,49)</f>
         <v/>
       </c>
-      <c r="BA7" s="81">
+      <c r="BA7" s="82">
         <f>EDATE($B$4,50)</f>
         <v/>
       </c>
-      <c r="BB7" s="81">
+      <c r="BB7" s="82">
         <f>EDATE($B$4,51)</f>
         <v/>
       </c>
-      <c r="BC7" s="81">
+      <c r="BC7" s="82">
         <f>EDATE($B$4,52)</f>
         <v/>
       </c>
-      <c r="BD7" s="81">
+      <c r="BD7" s="82">
         <f>EDATE($B$4,53)</f>
         <v/>
       </c>
-      <c r="BE7" s="81">
+      <c r="BE7" s="82">
         <f>EDATE($B$4,54)</f>
         <v/>
       </c>
-      <c r="BF7" s="81">
+      <c r="BF7" s="82">
         <f>EDATE($B$4,55)</f>
         <v/>
       </c>
-      <c r="BG7" s="81">
+      <c r="BG7" s="82">
         <f>EDATE($B$4,56)</f>
         <v/>
       </c>
-      <c r="BH7" s="81">
+      <c r="BH7" s="82">
         <f>EDATE($B$4,57)</f>
         <v/>
       </c>
-      <c r="BI7" s="81">
+      <c r="BI7" s="82">
         <f>EDATE($B$4,58)</f>
         <v/>
       </c>
-      <c r="BJ7" s="81">
+      <c r="BJ7" s="82">
         <f>EDATE($B$4,59)</f>
         <v/>
       </c>
-      <c r="BK7" s="81">
+      <c r="BK7" s="82">
         <f>EDATE($B$4,60)</f>
         <v/>
       </c>
-      <c r="BL7" s="81">
+      <c r="BL7" s="82">
         <f>EDATE($B$4,61)</f>
         <v/>
       </c>
-      <c r="BM7" s="81">
+      <c r="BM7" s="82">
         <f>EDATE($B$4,62)</f>
         <v/>
       </c>
-      <c r="BN7" s="81">
+      <c r="BN7" s="82">
         <f>EDATE($B$4,63)</f>
         <v/>
       </c>
-      <c r="BO7" s="81">
+      <c r="BO7" s="82">
         <f>EDATE($B$4,64)</f>
         <v/>
       </c>
-      <c r="BP7" s="81">
+      <c r="BP7" s="82">
         <f>EDATE($B$4,65)</f>
         <v/>
       </c>
-      <c r="BQ7" s="81">
+      <c r="BQ7" s="82">
         <f>EDATE($B$4,66)</f>
         <v/>
       </c>
-      <c r="BR7" s="81">
+      <c r="BR7" s="82">
         <f>EDATE($B$4,67)</f>
         <v/>
       </c>
-      <c r="BS7" s="81">
+      <c r="BS7" s="82">
         <f>EDATE($B$4,68)</f>
         <v/>
       </c>
-      <c r="BT7" s="81">
+      <c r="BT7" s="82">
         <f>EDATE($B$4,69)</f>
         <v/>
       </c>
-      <c r="BU7" s="81">
+      <c r="BU7" s="82">
         <f>EDATE($B$4,70)</f>
         <v/>
       </c>
-      <c r="BV7" s="81">
+      <c r="BV7" s="82">
         <f>EDATE($B$4,71)</f>
         <v/>
       </c>
-      <c r="BW7" s="81">
+      <c r="BW7" s="82">
         <f>EDATE($B$4,72)</f>
         <v/>
       </c>
-      <c r="BX7" s="81">
+      <c r="BX7" s="82">
         <f>EDATE($B$4,73)</f>
         <v/>
       </c>
-      <c r="BY7" s="81">
+      <c r="BY7" s="82">
         <f>EDATE($B$4,74)</f>
         <v/>
       </c>
-      <c r="BZ7" s="81">
+      <c r="BZ7" s="82">
         <f>EDATE($B$4,75)</f>
         <v/>
       </c>
-      <c r="CA7" s="81">
+      <c r="CA7" s="82">
         <f>EDATE($B$4,76)</f>
         <v/>
       </c>
-      <c r="CB7" s="81">
+      <c r="CB7" s="82">
         <f>EDATE($B$4,77)</f>
         <v/>
       </c>
-      <c r="CC7" s="81">
+      <c r="CC7" s="82">
         <f>EDATE($B$4,78)</f>
         <v/>
       </c>
-      <c r="CD7" s="81">
+      <c r="CD7" s="82">
         <f>EDATE($B$4,79)</f>
         <v/>
       </c>
-      <c r="CE7" s="81">
+      <c r="CE7" s="82">
         <f>EDATE($B$4,80)</f>
         <v/>
       </c>
-      <c r="CF7" s="81">
+      <c r="CF7" s="82">
         <f>EDATE($B$4,81)</f>
         <v/>
       </c>
-      <c r="CG7" s="81">
+      <c r="CG7" s="82">
         <f>EDATE($B$4,82)</f>
         <v/>
       </c>
-      <c r="CH7" s="81">
+      <c r="CH7" s="82">
         <f>EDATE($B$4,83)</f>
         <v/>
       </c>
-      <c r="CI7" s="81">
+      <c r="CI7" s="82">
         <f>EDATE($B$4,84)</f>
         <v/>
       </c>
-      <c r="CJ7" s="81">
+      <c r="CJ7" s="82">
         <f>EDATE($B$4,85)</f>
         <v/>
       </c>
-      <c r="CK7" s="81">
+      <c r="CK7" s="82">
         <f>EDATE($B$4,86)</f>
         <v/>
       </c>
-      <c r="CL7" s="81">
+      <c r="CL7" s="82">
         <f>EDATE($B$4,87)</f>
         <v/>
       </c>
-      <c r="CM7" s="81">
+      <c r="CM7" s="82">
         <f>EDATE($B$4,88)</f>
         <v/>
       </c>
-      <c r="CN7" s="81">
+      <c r="CN7" s="82">
         <f>EDATE($B$4,89)</f>
         <v/>
       </c>
-      <c r="CO7" s="81">
+      <c r="CO7" s="82">
         <f>EDATE($B$4,90)</f>
         <v/>
       </c>
-      <c r="CP7" s="81">
+      <c r="CP7" s="82">
         <f>EDATE($B$4,91)</f>
         <v/>
       </c>
-      <c r="CQ7" s="81">
+      <c r="CQ7" s="82">
         <f>EDATE($B$4,92)</f>
         <v/>
       </c>
-      <c r="CR7" s="81">
+      <c r="CR7" s="82">
         <f>EDATE($B$4,93)</f>
         <v/>
       </c>
-      <c r="CS7" s="81">
+      <c r="CS7" s="82">
         <f>EDATE($B$4,94)</f>
         <v/>
       </c>
-      <c r="CT7" s="81">
+      <c r="CT7" s="82">
         <f>EDATE($B$4,95)</f>
         <v/>
       </c>
-      <c r="CU7" s="81">
+      <c r="CU7" s="82">
         <f>EDATE($B$4,96)</f>
         <v/>
       </c>
-      <c r="CV7" s="81">
+      <c r="CV7" s="82">
         <f>EDATE($B$4,97)</f>
         <v/>
       </c>
-      <c r="CW7" s="81">
+      <c r="CW7" s="82">
         <f>EDATE($B$4,98)</f>
         <v/>
       </c>
-      <c r="CX7" s="81">
+      <c r="CX7" s="82">
         <f>EDATE($B$4,99)</f>
         <v/>
       </c>
-      <c r="CY7" s="81">
+      <c r="CY7" s="82">
         <f>EDATE($B$4,100)</f>
         <v/>
       </c>
-      <c r="CZ7" s="81">
+      <c r="CZ7" s="82">
         <f>EDATE($B$4,101)</f>
         <v/>
       </c>
-      <c r="DA7" s="81">
+      <c r="DA7" s="82">
         <f>EDATE($B$4,102)</f>
         <v/>
       </c>
-      <c r="DB7" s="81">
+      <c r="DB7" s="82">
         <f>EDATE($B$4,103)</f>
         <v/>
       </c>
-      <c r="DC7" s="81">
+      <c r="DC7" s="82">
         <f>EDATE($B$4,104)</f>
         <v/>
       </c>
-      <c r="DD7" s="81">
+      <c r="DD7" s="82">
         <f>EDATE($B$4,105)</f>
         <v/>
       </c>
-      <c r="DE7" s="81">
+      <c r="DE7" s="82">
         <f>EDATE($B$4,106)</f>
         <v/>
       </c>
-      <c r="DF7" s="81">
+      <c r="DF7" s="82">
         <f>EDATE($B$4,107)</f>
         <v/>
       </c>
-      <c r="DG7" s="81">
+      <c r="DG7" s="82">
         <f>EDATE($B$4,108)</f>
         <v/>
       </c>
-      <c r="DH7" s="81">
+      <c r="DH7" s="82">
         <f>EDATE($B$4,109)</f>
         <v/>
       </c>
-      <c r="DI7" s="81">
+      <c r="DI7" s="82">
         <f>EDATE($B$4,110)</f>
         <v/>
       </c>
-      <c r="DJ7" s="81">
+      <c r="DJ7" s="82">
         <f>EDATE($B$4,111)</f>
         <v/>
       </c>
-      <c r="DK7" s="81">
+      <c r="DK7" s="82">
         <f>EDATE($B$4,112)</f>
         <v/>
       </c>
-      <c r="DL7" s="81">
+      <c r="DL7" s="82">
         <f>EDATE($B$4,113)</f>
         <v/>
       </c>
-      <c r="DM7" s="81">
+      <c r="DM7" s="82">
         <f>EDATE($B$4,114)</f>
         <v/>
       </c>
-      <c r="DN7" s="81">
+      <c r="DN7" s="82">
         <f>EDATE($B$4,115)</f>
         <v/>
       </c>
-      <c r="DO7" s="81">
+      <c r="DO7" s="82">
         <f>EDATE($B$4,116)</f>
         <v/>
       </c>
-      <c r="DP7" s="81">
+      <c r="DP7" s="82">
         <f>EDATE($B$4,117)</f>
         <v/>
       </c>
-      <c r="DQ7" s="81">
+      <c r="DQ7" s="82">
         <f>EDATE($B$4,118)</f>
         <v/>
       </c>
-      <c r="DR7" s="81">
+      <c r="DR7" s="82">
         <f>EDATE($B$4,119)</f>
         <v/>
       </c>
@@ -6252,157 +6391,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B1" s="82" t="inlineStr">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="82" t="inlineStr">
+      <c r="C1" s="83" t="inlineStr">
         <is>
           <t>UnitType</t>
         </is>
       </c>
-      <c r="D1" s="82" t="inlineStr">
+      <c r="D1" s="83" t="inlineStr">
         <is>
           <t>RentBasis</t>
         </is>
       </c>
-      <c r="E1" s="82" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>YesNo</t>
         </is>
       </c>
-      <c r="F1" s="82" t="inlineStr">
+      <c r="F1" s="83" t="inlineStr">
         <is>
           <t>RentType</t>
         </is>
       </c>
-      <c r="G1" s="82" t="inlineStr">
+      <c r="G1" s="83" t="inlineStr">
         <is>
           <t>CostCurve</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="83" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>RAD 1</t>
         </is>
       </c>
-      <c r="B2" s="83" t="inlineStr">
+      <c r="B2" s="84" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="C2" s="83" t="inlineStr">
+      <c r="C2" s="84" t="inlineStr">
         <is>
           <t>Studio</t>
         </is>
       </c>
-      <c r="D2" s="83" t="inlineStr">
+      <c r="D2" s="84" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="E2" s="83" t="inlineStr">
+      <c r="E2" s="84" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="83" t="inlineStr">
+      <c r="F2" s="84" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="G2" s="83" t="inlineStr">
+      <c r="G2" s="84" t="inlineStr">
         <is>
           <t>S-curve</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="83" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>RAD 2</t>
         </is>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="C3" s="83" t="inlineStr">
+      <c r="C3" s="84" t="inlineStr">
         <is>
           <t>1 Bedroom</t>
         </is>
       </c>
-      <c r="D3" s="83" t="inlineStr">
+      <c r="D3" s="84" t="inlineStr">
         <is>
           <t>Live Local</t>
         </is>
       </c>
-      <c r="E3" s="83" t="inlineStr">
+      <c r="E3" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F3" s="83" t="inlineStr">
+      <c r="F3" s="84" t="inlineStr">
         <is>
           <t>Gross</t>
         </is>
       </c>
-      <c r="G3" s="83" t="inlineStr">
+      <c r="G3" s="84" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="83" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>Live Local A</t>
         </is>
       </c>
-      <c r="C4" s="83" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>2 Bedroom</t>
         </is>
       </c>
-      <c r="D4" s="83" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>LIHTC</t>
         </is>
       </c>
-      <c r="G4" s="83" t="inlineStr">
+      <c r="G4" s="84" t="inlineStr">
         <is>
           <t>Front-loaded</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="83" t="inlineStr">
+      <c r="C5" s="84" t="inlineStr">
         <is>
           <t>3 Bedroom</t>
         </is>
       </c>
-      <c r="D5" s="83" t="inlineStr">
+      <c r="D5" s="84" t="inlineStr">
         <is>
           <t>PBV</t>
         </is>
       </c>
-      <c r="G5" s="83" t="inlineStr">
+      <c r="G5" s="84" t="inlineStr">
         <is>
           <t>Back-loaded</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="83" t="inlineStr">
+      <c r="D6" s="84" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -6420,383 +6559,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV3"/>
+  <dimension ref="A1:BW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>ARCHIVE  -  purged records (FIFO overflow). Recoverable, not hard-deleted.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="85" t="inlineStr">
         <is>
           <t>RecordID</t>
         </is>
       </c>
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="85" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C3" s="84" t="inlineStr">
+      <c r="C3" s="85" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D3" s="84" t="inlineStr">
+      <c r="D3" s="85" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="E3" s="84" t="inlineStr">
+      <c r="E3" s="85" t="inlineStr">
         <is>
           <t>UpdatedBy</t>
         </is>
       </c>
-      <c r="F3" s="84" t="inlineStr">
+      <c r="F3" s="85" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="G3" s="84" t="inlineStr">
+      <c r="G3" s="85" t="inlineStr">
         <is>
           <t>PhaseNo</t>
         </is>
       </c>
-      <c r="H3" s="84" t="inlineStr">
+      <c r="H3" s="85" t="inlineStr">
         <is>
           <t>ProjectName</t>
         </is>
       </c>
-      <c r="I3" s="84" t="inlineStr">
+      <c r="I3" s="85" t="inlineStr">
         <is>
           <t>LandAcres</t>
         </is>
       </c>
-      <c r="J3" s="84" t="inlineStr">
+      <c r="J3" s="85" t="inlineStr">
         <is>
           <t>ClosingDate</t>
         </is>
       </c>
-      <c r="K3" s="84" t="inlineStr">
+      <c r="K3" s="85" t="inlineStr">
         <is>
           <t>GSF</t>
         </is>
       </c>
-      <c r="L3" s="84" t="inlineStr">
+      <c r="L3" s="85" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="M3" s="84" t="inlineStr">
+      <c r="M3" s="85" t="inlineStr">
+        <is>
+          <t>ExitCapRate</t>
+        </is>
+      </c>
+      <c r="N3" s="85" t="inlineStr">
         <is>
           <t>off_ConstStart</t>
         </is>
       </c>
-      <c r="N3" s="84" t="inlineStr">
+      <c r="O3" s="85" t="inlineStr">
         <is>
           <t>off_InitOcc</t>
         </is>
       </c>
-      <c r="O3" s="84" t="inlineStr">
+      <c r="P3" s="85" t="inlineStr">
         <is>
           <t>off_ConstEnd</t>
         </is>
       </c>
-      <c r="P3" s="84" t="inlineStr">
+      <c r="Q3" s="85" t="inlineStr">
         <is>
           <t>off_Stab</t>
         </is>
       </c>
-      <c r="Q3" s="84" t="inlineStr">
+      <c r="R3" s="85" t="inlineStr">
         <is>
           <t>HasCommercial</t>
         </is>
       </c>
-      <c r="R3" s="84" t="inlineStr">
+      <c r="S3" s="85" t="inlineStr">
         <is>
           <t>CommSF</t>
         </is>
       </c>
-      <c r="S3" s="84" t="inlineStr">
+      <c r="T3" s="85" t="inlineStr">
         <is>
           <t>CommRentPSF</t>
         </is>
       </c>
-      <c r="T3" s="84" t="inlineStr">
+      <c r="U3" s="85" t="inlineStr">
         <is>
           <t>CommEscalation</t>
         </is>
       </c>
-      <c r="U3" s="84" t="inlineStr">
+      <c r="V3" s="85" t="inlineStr">
         <is>
           <t>CommAbatement</t>
         </is>
       </c>
-      <c r="V3" s="84" t="inlineStr">
+      <c r="W3" s="85" t="inlineStr">
         <is>
           <t>CommVacancy</t>
         </is>
       </c>
-      <c r="W3" s="84" t="inlineStr">
+      <c r="X3" s="85" t="inlineStr">
         <is>
           <t>CommOpExPSF</t>
         </is>
       </c>
-      <c r="X3" s="84" t="inlineStr">
+      <c r="Y3" s="85" t="inlineStr">
         <is>
           <t>UM1_Type</t>
         </is>
       </c>
-      <c r="Y3" s="84" t="inlineStr">
+      <c r="Z3" s="85" t="inlineStr">
         <is>
           <t>UM1_Count</t>
         </is>
       </c>
-      <c r="Z3" s="84" t="inlineStr">
+      <c r="AA3" s="85" t="inlineStr">
         <is>
           <t>UM1_AvgSF</t>
         </is>
       </c>
-      <c r="AA3" s="84" t="inlineStr">
+      <c r="AB3" s="85" t="inlineStr">
         <is>
           <t>UM1_PUPM</t>
         </is>
       </c>
-      <c r="AB3" s="84" t="inlineStr">
+      <c r="AC3" s="85" t="inlineStr">
         <is>
           <t>UM2_Type</t>
         </is>
       </c>
-      <c r="AC3" s="84" t="inlineStr">
+      <c r="AD3" s="85" t="inlineStr">
         <is>
           <t>UM2_Count</t>
         </is>
       </c>
-      <c r="AD3" s="84" t="inlineStr">
+      <c r="AE3" s="85" t="inlineStr">
         <is>
           <t>UM2_AvgSF</t>
         </is>
       </c>
-      <c r="AE3" s="84" t="inlineStr">
+      <c r="AF3" s="85" t="inlineStr">
         <is>
           <t>UM2_PUPM</t>
         </is>
       </c>
-      <c r="AF3" s="84" t="inlineStr">
+      <c r="AG3" s="85" t="inlineStr">
         <is>
           <t>UM3_Type</t>
         </is>
       </c>
-      <c r="AG3" s="84" t="inlineStr">
+      <c r="AH3" s="85" t="inlineStr">
         <is>
           <t>UM3_Count</t>
         </is>
       </c>
-      <c r="AH3" s="84" t="inlineStr">
+      <c r="AI3" s="85" t="inlineStr">
         <is>
           <t>UM3_AvgSF</t>
         </is>
       </c>
-      <c r="AI3" s="84" t="inlineStr">
+      <c r="AJ3" s="85" t="inlineStr">
         <is>
           <t>UM3_PUPM</t>
         </is>
       </c>
-      <c r="AJ3" s="84" t="inlineStr">
+      <c r="AK3" s="85" t="inlineStr">
         <is>
           <t>UM4_Type</t>
         </is>
       </c>
-      <c r="AK3" s="84" t="inlineStr">
+      <c r="AL3" s="85" t="inlineStr">
         <is>
           <t>UM4_Count</t>
         </is>
       </c>
-      <c r="AL3" s="84" t="inlineStr">
+      <c r="AM3" s="85" t="inlineStr">
         <is>
           <t>UM4_AvgSF</t>
         </is>
       </c>
-      <c r="AM3" s="84" t="inlineStr">
+      <c r="AN3" s="85" t="inlineStr">
         <is>
           <t>UM4_PUPM</t>
         </is>
       </c>
-      <c r="AN3" s="84" t="inlineStr">
+      <c r="AO3" s="85" t="inlineStr">
         <is>
           <t>ResVacancy</t>
         </is>
       </c>
-      <c r="AO3" s="84" t="inlineStr">
+      <c r="AP3" s="85" t="inlineStr">
         <is>
           <t>ResConcessions</t>
         </is>
       </c>
-      <c r="AP3" s="84" t="inlineStr">
+      <c r="AQ3" s="85" t="inlineStr">
         <is>
           <t>ResModel</t>
         </is>
       </c>
-      <c r="AQ3" s="84" t="inlineStr">
+      <c r="AR3" s="85" t="inlineStr">
         <is>
           <t>ResCollLoss</t>
         </is>
       </c>
-      <c r="AR3" s="84" t="inlineStr">
+      <c r="AS3" s="85" t="inlineStr">
         <is>
           <t>OI1_Name</t>
         </is>
       </c>
-      <c r="AS3" s="84" t="inlineStr">
+      <c r="AT3" s="85" t="inlineStr">
         <is>
           <t>OI1_PUPM</t>
         </is>
       </c>
-      <c r="AT3" s="84" t="inlineStr">
+      <c r="AU3" s="85" t="inlineStr">
         <is>
           <t>OI2_Name</t>
         </is>
       </c>
-      <c r="AU3" s="84" t="inlineStr">
+      <c r="AV3" s="85" t="inlineStr">
         <is>
           <t>OI2_PUPM</t>
         </is>
       </c>
-      <c r="AV3" s="84" t="inlineStr">
+      <c r="AW3" s="85" t="inlineStr">
         <is>
           <t>OI3_Name</t>
         </is>
       </c>
-      <c r="AW3" s="84" t="inlineStr">
+      <c r="AX3" s="85" t="inlineStr">
         <is>
           <t>OI3_PUPM</t>
         </is>
       </c>
-      <c r="AX3" s="84" t="inlineStr">
+      <c r="AY3" s="85" t="inlineStr">
         <is>
           <t>OI4_Name</t>
         </is>
       </c>
-      <c r="AY3" s="84" t="inlineStr">
+      <c r="AZ3" s="85" t="inlineStr">
         <is>
           <t>OI4_PUPM</t>
         </is>
       </c>
-      <c r="AZ3" s="84" t="inlineStr">
+      <c r="BA3" s="85" t="inlineStr">
         <is>
           <t>OI5_Name</t>
         </is>
       </c>
-      <c r="BA3" s="84" t="inlineStr">
+      <c r="BB3" s="85" t="inlineStr">
         <is>
           <t>OI5_PUPM</t>
         </is>
       </c>
-      <c r="BB3" s="84" t="inlineStr">
+      <c r="BC3" s="85" t="inlineStr">
         <is>
           <t>OpEx_Payroll</t>
         </is>
       </c>
-      <c r="BC3" s="84" t="inlineStr">
+      <c r="BD3" s="85" t="inlineStr">
         <is>
           <t>OpEx_Marketing</t>
         </is>
       </c>
-      <c r="BD3" s="84" t="inlineStr">
+      <c r="BE3" s="85" t="inlineStr">
         <is>
           <t>OpEx_Admin</t>
         </is>
       </c>
-      <c r="BE3" s="84" t="inlineStr">
+      <c r="BF3" s="85" t="inlineStr">
         <is>
           <t>OpEx_ProfFees</t>
         </is>
       </c>
-      <c r="BF3" s="84" t="inlineStr">
+      <c r="BG3" s="85" t="inlineStr">
         <is>
           <t>OpEx_RM</t>
         </is>
       </c>
-      <c r="BG3" s="84" t="inlineStr">
+      <c r="BH3" s="85" t="inlineStr">
         <is>
           <t>OpEx_Utilities</t>
         </is>
       </c>
-      <c r="BH3" s="84" t="inlineStr">
+      <c r="BI3" s="85" t="inlineStr">
         <is>
           <t>OpEx_Insurance</t>
         </is>
       </c>
-      <c r="BI3" s="84" t="inlineStr">
+      <c r="BJ3" s="85" t="inlineStr">
         <is>
           <t>OpEx_RETaxes</t>
         </is>
       </c>
-      <c r="BJ3" s="84" t="inlineStr">
+      <c r="BK3" s="85" t="inlineStr">
         <is>
           <t>OpEx_MgmtFeePct</t>
         </is>
       </c>
-      <c r="BK3" s="84" t="inlineStr">
+      <c r="BL3" s="85" t="inlineStr">
         <is>
           <t>Bud_Land</t>
         </is>
       </c>
-      <c r="BL3" s="84" t="inlineStr">
+      <c r="BM3" s="85" t="inlineStr">
         <is>
           <t>Bud_Shell</t>
         </is>
       </c>
-      <c r="BM3" s="84" t="inlineStr">
+      <c r="BN3" s="85" t="inlineStr">
         <is>
           <t>Bud_Sitework</t>
         </is>
       </c>
-      <c r="BN3" s="84" t="inlineStr">
+      <c r="BO3" s="85" t="inlineStr">
         <is>
           <t>Bud_Parking</t>
         </is>
       </c>
-      <c r="BO3" s="84" t="inlineStr">
+      <c r="BP3" s="85" t="inlineStr">
         <is>
           <t>Bud_FFE</t>
         </is>
       </c>
-      <c r="BP3" s="84" t="inlineStr">
+      <c r="BQ3" s="85" t="inlineStr">
         <is>
           <t>Bud_GCFee</t>
         </is>
       </c>
-      <c r="BQ3" s="84" t="inlineStr">
+      <c r="BR3" s="85" t="inlineStr">
         <is>
           <t>Bud_AE</t>
         </is>
       </c>
-      <c r="BR3" s="84" t="inlineStr">
+      <c r="BS3" s="85" t="inlineStr">
         <is>
           <t>Bud_Permits</t>
         </is>
       </c>
-      <c r="BS3" s="84" t="inlineStr">
+      <c r="BT3" s="85" t="inlineStr">
         <is>
           <t>Bud_Legal</t>
         </is>
       </c>
-      <c r="BT3" s="84" t="inlineStr">
+      <c r="BU3" s="85" t="inlineStr">
         <is>
           <t>Bud_Mktg</t>
         </is>
       </c>
-      <c r="BU3" s="84" t="inlineStr">
+      <c r="BV3" s="85" t="inlineStr">
         <is>
           <t>Bud_DevFee</t>
         </is>
       </c>
-      <c r="BV3" s="84" t="inlineStr">
+      <c r="BW3" s="85" t="inlineStr">
         <is>
           <t>Bud_TaxIns</t>
         </is>
